--- a/resultados/rodada03/cenarios_exemplo.xlsx
+++ b/resultados/rodada03/cenarios_exemplo.xlsx
@@ -449,7 +449,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cenários: /home/user/MIP-desagregacao/parametros/cenarios_exemplo.csv. Versões: original = original; v01 = /home/user/MIP-desagregacao/resultados/rodada02/MIP_RS_RB_2019_S38_11sub_v01.xlsx; v02 = /home/user/MIP-desagregacao/resultados/rodada03/MIP_RS_RB_2019_S38_11sub_v02.xlsx</t>
+          <t>Cenários: /tmp/claude-0/-home-user-MIP-desagregacao/21fc59b7-f453-5721-8bf4-b4ad09df36f2/scratchpad/wt/parametros/cenarios_exemplo.csv. Versões: original = original; v01 = /tmp/claude-0/-home-user-MIP-desagregacao/21fc59b7-f453-5721-8bf4-b4ad09df36f2/scratchpad/wt/resultados/rodada02/MIP_RS_RB_2019_S38_11sub_v01.xlsx; v02 = /tmp/claude-0/-home-user-MIP-desagregacao/21fc59b7-f453-5721-8bf4-b4ad09df36f2/scratchpad/wt/resultados/rodada03/MIP_RS_RB_2019_S38_11sub_v02.xlsx</t>
         </is>
       </c>
     </row>
@@ -1748,52 +1748,52 @@
         <v>1000</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1909.201857117318</v>
+        <v>1907.266107766158</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1381.836663304188</v>
+        <v>1383.133752563955</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>527.3651938131304</v>
+        <v>524.1323552022034</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>382420.1666023621</v>
+        <v>383167.5996365633</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>282974.4314910982</v>
+        <v>283630.2800182434</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>99445.73511126394</v>
+        <v>99537.31961831992</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>200.3036845877438</v>
+        <v>200.8988667477238</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4.992419395869605</v>
+        <v>4.977628874610514</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>73.99568751962109</v>
+        <v>74.02251137290011</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>26.00431248037894</v>
+        <v>25.97748862709991</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>130480.771620463</v>
+        <v>130486.0827273468</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>251939.394981899</v>
+        <v>252681.5169092165</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>65.88025867471156</v>
+        <v>65.9454288799174</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>3704.079094884406</v>
+        <v>3701.95485690463</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>2.061934893239426</v>
+        <v>2.057809168115604</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>48.51890324169861</v>
+        <v>48.57073231935405</v>
       </c>
     </row>
     <row r="21">
@@ -1811,52 +1811,52 @@
         <v>1000</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1954.42507915745</v>
+        <v>1953.868610209056</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1398.586171388512</v>
+        <v>1398.956195226613</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>555.8389077689386</v>
+        <v>554.9124149824435</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>202149.1515720201</v>
+        <v>202360.3016291293</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>125166.0302746638</v>
+        <v>125353.1212499976</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>76983.12129735632</v>
+        <v>77007.18037913172</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>103.4315173949601</v>
+        <v>103.5690427553762</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>9.668232906043848</v>
+        <v>9.65539483030599</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>61.91766292428422</v>
+        <v>61.9455101819997</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>38.08233707571578</v>
+        <v>38.05448981800031</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>60372.1001488947</v>
+        <v>60373.69348095982</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>141777.0514231254</v>
+        <v>141986.6081481695</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>70.13487334504799</v>
+        <v>70.16524832444252</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>9622.83901407904</v>
+        <v>9622.225269525754</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>4.307353992646417</v>
+        <v>4.306172141541373</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>52.39458487353753</v>
+        <v>52.40893833359175</v>
       </c>
     </row>
     <row r="22">
@@ -1874,52 +1874,52 @@
         <v>1000</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2114.958163480926</v>
+        <v>2114.283881159667</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1381.930314210203</v>
+        <v>1382.385988666276</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>733.0278492707229</v>
+        <v>731.8978924933913</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>339952.7654894255</v>
+        <v>340218.1474261827</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>257341.4658703298</v>
+        <v>257571.8751482602</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>82611.29961909569</v>
+        <v>82646.27227792254</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>160.7373476030896</v>
+        <v>160.9141281631377</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>6.221329485100815</v>
+        <v>6.214494720974295</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>75.69918294379477</v>
+        <v>75.70785894192952</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>24.30081705620524</v>
+        <v>24.2921410580705</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>178331.2335273424</v>
+        <v>178333.0924147516</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>161621.5319620831</v>
+        <v>161885.0550114311</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>47.54234951711563</v>
+        <v>47.58272192007493</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>6093.479727533617</v>
+        <v>6092.743972529101</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>11.32297350211164</v>
+        <v>11.32153073903026</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>97.87629849462417</v>
+        <v>97.89509101845073</v>
       </c>
     </row>
     <row r="23">
@@ -1937,52 +1937,52 @@
         <v>1000</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1917.582693290566</v>
+        <v>1917.285510400524</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1403.365265473746</v>
+        <v>1403.565424091987</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>514.2174278168201</v>
+        <v>513.7200863085366</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>208859.630790865</v>
+        <v>208975.7151938569</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>144213.466990081</v>
+        <v>144314.675025019</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>64646.16380078402</v>
+        <v>64661.04016883792</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>108.9181872164598</v>
+        <v>108.9956159686418</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>9.181203117277731</v>
+        <v>9.174680936595664</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>69.04803309476527</v>
+        <v>69.05810796778231</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>30.95196690523475</v>
+        <v>30.94189203221768</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>92228.50207456989</v>
+        <v>92229.38725905052</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>116631.1287162951</v>
+        <v>116746.3279348064</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>55.8418724933398</v>
+        <v>55.86597841117871</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>10771.80192826965</v>
+        <v>10771.47691968621</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>4.759078576482628</v>
+        <v>4.758443681425891</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>71.50936990028188</v>
+        <v>71.51752319984799</v>
       </c>
     </row>
     <row r="24">
@@ -2000,52 +2000,52 @@
         <v>1000</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1966.609134609069</v>
+        <v>1966.35911009856</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1399.981978432327</v>
+        <v>1400.151277335299</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>566.6271561767422</v>
+        <v>566.2078327632615</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>161531.3544111279</v>
+        <v>161630.1940950605</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>86738.10448239293</v>
+        <v>86823.71006856073</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>74793.24992873499</v>
+        <v>74806.48402649975</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>82.13698979041801</v>
+        <v>82.19769891724359</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>12.17478267162718</v>
+        <v>12.1657906872405</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>53.69737955742512</v>
+        <v>53.71750653067743</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>46.30262044257488</v>
+        <v>46.28249346932256</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>40826.46614562507</v>
+        <v>40827.26281165763</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>120704.8882655028</v>
+        <v>120802.9312834029</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>74.72536134271866</v>
+        <v>74.7403243309566</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>11054.64630512914</v>
+        <v>11054.37384916945</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>4.860327775129886</v>
+        <v>4.859792308038282</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>53.99692550424508</v>
+        <v>54.00395783543333</v>
       </c>
     </row>
     <row r="25">
@@ -2063,52 +2063,52 @@
         <v>1000</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1952.261629532552</v>
+        <v>1951.406037229921</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1406.888618608744</v>
+        <v>1407.460208297674</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>545.3730109238079</v>
+        <v>543.9458289322461</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>288882.375197493</v>
+        <v>289210.4983443036</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>210554.046905864</v>
+        <v>210843.0576271448</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>78328.32829162902</v>
+        <v>78367.44071715878</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>147.9731870090909</v>
+        <v>148.2062127648465</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>6.757981092470243</v>
+        <v>6.747355467389646</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>72.88573654308946</v>
+        <v>72.90297511127595</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>27.11426345691053</v>
+        <v>27.09702488872405</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>122117.5116210804</v>
+        <v>122119.9016191781</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>166764.8635764127</v>
+        <v>167090.5967251255</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>57.7276005372099</v>
+        <v>57.7747342097537</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>8271.662985076875</v>
+        <v>8270.722218562336</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>4.028248316672186</v>
+        <v>4.026427278222913</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>72.47195032017014</v>
+        <v>72.49452952571609</v>
       </c>
     </row>
     <row r="26">
@@ -2126,52 +2126,52 @@
         <v>1000</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1942.464721194208</v>
+        <v>1941.512830001077</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1399.451525393135</v>
+        <v>1400.08779552882</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>543.0131958010727</v>
+        <v>541.4250344722572</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>281148.8412345927</v>
+        <v>281514.3472652387</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>200128.0099419135</v>
+        <v>200449.7253461142</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>81020.83129267913</v>
+        <v>81064.62191912456</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>144.7381968727572</v>
+        <v>144.9974179491168</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>6.909026239142138</v>
+        <v>6.896674534928096</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>71.18222826852245</v>
+        <v>71.20408863469163</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>28.81777173147754</v>
+        <v>28.79591136530838</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>107532.294217767</v>
+        <v>107534.9497712089</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>173616.5470168256</v>
+        <v>173979.3974940298</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>61.75253871025515</v>
+        <v>61.80125424659402</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>7836.038304389906</v>
+        <v>7834.99202846594</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>3.74977192431714</v>
+        <v>3.747745416564731</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>63.37592565362624</v>
+        <v>63.40111260549658</v>
       </c>
     </row>
     <row r="27">
@@ -2189,52 +2189,52 @@
         <v>999.9999999999998</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2105.157716599519</v>
+        <v>2104.513936999524</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1400.50743876489</v>
+        <v>1400.941647904692</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>704.650277834629</v>
+        <v>703.5722890948318</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>366364.5005821656</v>
+        <v>366616.7671589081</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>287678.7192170005</v>
+        <v>287898.273329167</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>78685.78136516512</v>
+        <v>78718.49382974101</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>174.0318540949785</v>
+        <v>174.2049604487798</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>5.746074505729546</v>
+        <v>5.740364668284071</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>78.52254210216036</v>
+        <v>78.52839780357866</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>21.47745789783966</v>
+        <v>21.47160219642134</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>206819.2000511457</v>
+        <v>206820.9704201069</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>159545.3005310199</v>
+        <v>159795.7967388011</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>43.54824233174804</v>
+        <v>43.58660351983806</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>6784.30799047617</v>
+        <v>6783.604595166011</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>10.47565804818722</v>
+        <v>10.47428179802327</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>112.3901276188296</v>
+        <v>112.40790686915</v>
       </c>
     </row>
     <row r="28">
@@ -2252,52 +2252,52 @@
         <v>1000</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2065.96831397461</v>
+        <v>2065.002739618501</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1383.766174787601</v>
+        <v>1384.416032832909</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>682.2021391870086</v>
+        <v>680.5867067855913</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>352502.9992583847</v>
+        <v>352879.548248544</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>266356.2165165095</v>
+        <v>266684.8094360136</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>86146.78274187523</v>
+        <v>86194.73881253046</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>170.6236232540384</v>
+        <v>170.8857530686554</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>5.860853151096893</v>
+        <v>5.851862908654754</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>75.56140432191626</v>
+        <v>75.57389221326569</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>24.43859567808376</v>
+        <v>24.4261077867343</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>170014.9224014508</v>
+        <v>170017.5779548927</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>182488.0768569339</v>
+        <v>182861.9702936514</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>51.76922671320879</v>
+        <v>51.81994003371825</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>5605.035739543056</v>
+        <v>5603.979241147083</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>9.077332947982349</v>
+        <v>9.075270811716141</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>87.81095584802875</v>
+        <v>87.83735557373143</v>
       </c>
     </row>
   </sheetData>
@@ -12701,28 +12701,28 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>24.5854853165744</v>
+        <v>24.69463727684087</v>
       </c>
       <c r="I182" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>137373.0663280212</v>
+        <v>137982.9603075152</v>
       </c>
       <c r="K182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L182" s="2" t="n">
-        <v>35.92202460150612</v>
+        <v>36.01112422824708</v>
       </c>
       <c r="M182" s="2" t="n">
-        <v>15.75980730763606</v>
+        <v>15.82977598382447</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>0.2267656271348853</v>
+        <v>0.2277723964706991</v>
       </c>
       <c r="O182" s="2" t="n">
-        <v>17.02444631024794</v>
+        <v>17.1000295929567</v>
       </c>
     </row>
     <row r="183">
@@ -12755,25 +12755,25 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>970.2255008807361</v>
+        <v>974.5334493114932</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>971.1163916193452</v>
+        <v>975.429825520984</v>
       </c>
       <c r="I183" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>126747.6637116642</v>
+        <v>127310.642232391</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>126631.3868979727</v>
+        <v>127193.6494688663</v>
       </c>
       <c r="L183" s="2" t="n">
-        <v>33.1435616583096</v>
+        <v>33.22583703662467</v>
       </c>
       <c r="M183" s="2" t="n">
-        <v>747.4002125697967</v>
+        <v>750.7199602774991</v>
       </c>
       <c r="N183" s="2" t="n">
         <v>0</v>
@@ -12815,28 +12815,28 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>28.41344360645447</v>
+        <v>28.53769053024471</v>
       </c>
       <c r="I184" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>46469.9906252039</v>
+        <v>46673.1956102706</v>
       </c>
       <c r="K184" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L184" s="2" t="n">
-        <v>12.15155336552193</v>
+        <v>12.18088263583361</v>
       </c>
       <c r="M184" s="2" t="n">
-        <v>17.51112265616906</v>
+        <v>17.5876956739376</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>0.08890282259869514</v>
+        <v>0.08929157879372558</v>
       </c>
       <c r="O184" s="2" t="n">
-        <v>9.221917979931277</v>
+        <v>9.247038248925008</v>
       </c>
     </row>
     <row r="185">
@@ -12872,28 +12872,28 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>4.582912280468758</v>
+        <v>4.602952538901897</v>
       </c>
       <c r="I185" s="2" t="n">
         <v>4798.899130329469</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>21992.93375711776</v>
+        <v>22089.10493588414</v>
       </c>
       <c r="K185" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L185" s="2" t="n">
-        <v>5.750986919051753</v>
+        <v>5.764867634120365</v>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2.824435509377035</v>
+        <v>2.836786262363706</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>0.0209924663507988</v>
+        <v>0.0210842626639449</v>
       </c>
       <c r="O185" s="2" t="n">
-        <v>2.666565316804391</v>
+        <v>2.673828972607151</v>
       </c>
     </row>
     <row r="186">
@@ -12929,28 +12929,28 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>10.52146317696673</v>
+        <v>10.56747165983902</v>
       </c>
       <c r="I186" s="2" t="n">
         <v>924.0344320034608</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>9722.194250573781</v>
+        <v>9764.707672912016</v>
       </c>
       <c r="K186" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L186" s="2" t="n">
-        <v>2.542280742396845</v>
+        <v>2.548416850008691</v>
       </c>
       <c r="M186" s="2" t="n">
-        <v>6.484347155033948</v>
+        <v>6.512702049215725</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>0.009699695467756427</v>
+        <v>0.00974211050692813</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>1.35446946446574</v>
+        <v>1.387316273853757</v>
       </c>
     </row>
     <row r="187">
@@ -12986,28 +12986,28 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>22.16098781069714</v>
+        <v>22.2151983978338</v>
       </c>
       <c r="I187" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>9356.03929123532</v>
+        <v>9378.926194453898</v>
       </c>
       <c r="K187" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L187" s="2" t="n">
-        <v>2.446533971876977</v>
+        <v>2.447734673638863</v>
       </c>
       <c r="M187" s="2" t="n">
-        <v>166.1677295349942</v>
+        <v>166.5742118749605</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.001004488530424841</v>
+        <v>0.00100694572743571</v>
       </c>
       <c r="O187" s="2" t="n">
-        <v>4.151332359967861</v>
+        <v>4.161487420137364</v>
       </c>
     </row>
     <row r="188">
@@ -13043,28 +13043,28 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>11.70508039237595</v>
+        <v>11.60487581551754</v>
       </c>
       <c r="I188" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>5219.861238373764</v>
+        <v>5175.175173082702</v>
       </c>
       <c r="K188" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L188" s="2" t="n">
-        <v>1.364954490959505</v>
+        <v>1.350629640395322</v>
       </c>
       <c r="M188" s="2" t="n">
-        <v>121.825094767236</v>
+        <v>120.7821773619153</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>0.0004672034615092487</v>
+        <v>0.0004632038371070266</v>
       </c>
       <c r="O188" s="2" t="n">
-        <v>2.192667557239483</v>
+        <v>2.173896620398464</v>
       </c>
     </row>
     <row r="189">
@@ -13097,25 +13097,25 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>29.77449911926392</v>
+        <v>25.46655068850678</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>29.91380397165308</v>
+        <v>25.60212928579547</v>
       </c>
       <c r="I189" s="2" t="n">
         <v>129.2846172515396</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>3867.394697012754</v>
+        <v>3309.961485538501</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>3849.384722490339</v>
+        <v>3292.433258480532</v>
       </c>
       <c r="L189" s="2" t="n">
-        <v>1.01129465304429</v>
+        <v>0.8638416945164517</v>
       </c>
       <c r="M189" s="2" t="n">
-        <v>14.50021674107932</v>
+        <v>12.41020446710688</v>
       </c>
       <c r="N189" s="2" t="n">
         <v>0</v>
@@ -13157,28 +13157,28 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>2.003193852010858</v>
+        <v>2.012087413920466</v>
       </c>
       <c r="I190" s="2" t="n">
         <v>1387.165085961316</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>2778.760571921821</v>
+        <v>2791.097410492664</v>
       </c>
       <c r="K190" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L190" s="2" t="n">
-        <v>0.726625009504574</v>
+        <v>0.728427302605971</v>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1.284088912666261</v>
+        <v>1.289789870779114</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>0.01507861159528109</v>
+        <v>0.01514555597293028</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>0.9244300842011611</v>
+        <v>0.9285342682154512</v>
       </c>
     </row>
     <row r="191">
@@ -13214,28 +13214,28 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>5.5863489879047</v>
+        <v>5.596911769819069</v>
       </c>
       <c r="I191" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>2536.664767213388</v>
+        <v>2541.461144379217</v>
       </c>
       <c r="K191" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L191" s="2" t="n">
-        <v>0.6633187757200563</v>
+        <v>0.6632766305892794</v>
       </c>
       <c r="M191" s="2" t="n">
-        <v>35.92837732376666</v>
+        <v>35.99631142796061</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>0.004808341582610706</v>
+        <v>0.00481743329235116</v>
       </c>
       <c r="O191" s="2" t="n">
-        <v>0.4982189124281325</v>
+        <v>0.4991609548477856</v>
       </c>
     </row>
     <row r="192">
@@ -13271,28 +13271,28 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>7.463299186008487</v>
+        <v>7.494435935155344</v>
       </c>
       <c r="I192" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>41701.69028203929</v>
+        <v>41875.66897925486</v>
       </c>
       <c r="K192" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L192" s="2" t="n">
-        <v>20.62916908517528</v>
+        <v>20.69361858137641</v>
       </c>
       <c r="M192" s="2" t="n">
-        <v>4.784129966775019</v>
+        <v>4.804089270421951</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>0.06883816604057606</v>
+        <v>0.06912535762358983</v>
       </c>
       <c r="O192" s="2" t="n">
-        <v>5.168030431510807</v>
+        <v>5.189591360949485</v>
       </c>
     </row>
     <row r="193">
@@ -13325,25 +13325,25 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>291.0676502642208</v>
+        <v>292.3600347934479</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>294.3841229998835</v>
+        <v>295.6153781720723</v>
       </c>
       <c r="I193" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>38422.27373160027</v>
+        <v>38582.97405326573</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>37989.41606939181</v>
+        <v>38158.09484065988</v>
       </c>
       <c r="L193" s="2" t="n">
-        <v>19.00689339173976</v>
+        <v>19.06647387983128</v>
       </c>
       <c r="M193" s="2" t="n">
-        <v>226.5668235095859</v>
+        <v>227.5144343061528</v>
       </c>
       <c r="N193" s="2" t="n">
         <v>0</v>
@@ -13385,28 +13385,28 @@
         <v>50</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>84.18637844935719</v>
+        <v>84.20184907719651</v>
       </c>
       <c r="I194" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>35542.23626163415</v>
+        <v>35548.76773050012</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>21109.25598433646</v>
       </c>
       <c r="L194" s="2" t="n">
-        <v>17.58218423636146</v>
+        <v>17.56706599284044</v>
       </c>
       <c r="M194" s="2" t="n">
-        <v>631.247103432407</v>
+        <v>631.3631054411848</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>0.003815906235441589</v>
+        <v>0.003816607470799679</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>15.77030952368559</v>
+        <v>15.77320757672036</v>
       </c>
     </row>
     <row r="195">
@@ -13442,28 +13442,28 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>9.022297412332213</v>
+        <v>9.056968855859358</v>
       </c>
       <c r="I195" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>14755.90505593056</v>
+        <v>14812.60996217088</v>
       </c>
       <c r="K195" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L195" s="2" t="n">
-        <v>7.299513721022688</v>
+        <v>7.319918898578394</v>
       </c>
       <c r="M195" s="2" t="n">
-        <v>5.560415654507169</v>
+        <v>5.58178356431351</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>0.02822986602366733</v>
+        <v>0.02833834950197527</v>
       </c>
       <c r="O195" s="2" t="n">
-        <v>2.928292954542592</v>
+        <v>2.934720219938411</v>
       </c>
     </row>
     <row r="196">
@@ -13499,28 +13499,28 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>46.68810873985096</v>
+        <v>46.64858986891273</v>
       </c>
       <c r="I196" s="2" t="n">
         <v>243.170196149393</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>11353.15656011375</v>
+        <v>11343.54674851609</v>
       </c>
       <c r="K196" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L196" s="2" t="n">
-        <v>5.616227657561518</v>
+        <v>5.605618620447448</v>
       </c>
       <c r="M196" s="2" t="n">
-        <v>38.43454111404539</v>
+        <v>38.40200842615435</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0.04412822903130228</v>
+        <v>0.04409087695526215</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>5.562958261863566</v>
+        <v>5.558249529050885</v>
       </c>
     </row>
     <row r="197">
@@ -13556,28 +13556,28 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>16.10489915891709</v>
+        <v>16.07628770675517</v>
       </c>
       <c r="I197" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>7181.95313910916</v>
+        <v>7169.19390934677</v>
       </c>
       <c r="K197" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L197" s="2" t="n">
-        <v>3.552799051224526</v>
+        <v>3.542786728241751</v>
       </c>
       <c r="M197" s="2" t="n">
-        <v>167.6178890261856</v>
+        <v>167.3201044100864</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>0.0006428204149032881</v>
+        <v>0.0006416784005778196</v>
       </c>
       <c r="O197" s="2" t="n">
-        <v>3.016868634355701</v>
+        <v>3.011508961391661</v>
       </c>
     </row>
     <row r="198">
@@ -13613,28 +13613,28 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>1.455240631220989</v>
+        <v>1.460832920086885</v>
       </c>
       <c r="I198" s="2" t="n">
         <v>4798.899130329469</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>6983.552999586513</v>
+        <v>7010.389829761613</v>
       </c>
       <c r="K198" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L198" s="2" t="n">
-        <v>3.454653628411825</v>
+        <v>3.464310822490137</v>
       </c>
       <c r="M198" s="2" t="n">
-        <v>0.8968605685571626</v>
+        <v>0.9003070799204381</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>0.00666586836353262</v>
+        <v>0.006691484375504218</v>
       </c>
       <c r="O198" s="2" t="n">
-        <v>0.8467310647328182</v>
+        <v>0.8485895417897269</v>
       </c>
     </row>
     <row r="199">
@@ -13670,28 +13670,28 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>15.26095628712189</v>
+        <v>15.26394408666446</v>
       </c>
       <c r="I199" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>6929.737152358899</v>
+        <v>6931.093860621762</v>
       </c>
       <c r="K199" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L199" s="2" t="n">
-        <v>3.428031776769553</v>
+        <v>3.425125286344229</v>
       </c>
       <c r="M199" s="2" t="n">
-        <v>98.15022244266886</v>
+        <v>98.16943835445051</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>0.01313557224309673</v>
+        <v>0.01313814393362522</v>
       </c>
       <c r="O199" s="2" t="n">
-        <v>1.361049418939891</v>
+        <v>1.361315886044233</v>
       </c>
     </row>
     <row r="200">
@@ -13727,28 +13727,28 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>34.07776180508898</v>
+        <v>34.07759460036603</v>
       </c>
       <c r="I200" s="2" t="n">
         <v>149.0342130919736</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>5078.752414557148</v>
+        <v>5078.727495332839</v>
       </c>
       <c r="K200" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L200" s="2" t="n">
-        <v>2.512378793114909</v>
+        <v>2.509744971936614</v>
       </c>
       <c r="M200" s="2" t="n">
-        <v>43.39356417876146</v>
+        <v>43.39335126545696</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>0.02062098937908996</v>
+        <v>0.02062088820088361</v>
       </c>
       <c r="O200" s="2" t="n">
-        <v>0.8297714904854758</v>
+        <v>0.8297674191584631</v>
       </c>
     </row>
     <row r="201">
@@ -13784,28 +13784,28 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>4.6943417576596</v>
+        <v>4.692401962210954</v>
       </c>
       <c r="I201" s="2" t="n">
         <v>986.3644347220352</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>4630.331754185957</v>
+        <v>4628.418408944776</v>
       </c>
       <c r="K201" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L201" s="2" t="n">
-        <v>2.290552158234658</v>
+        <v>2.2872165991467</v>
       </c>
       <c r="M201" s="2" t="n">
-        <v>30.41707828627485</v>
+        <v>30.40450934411707</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>0.140409515392764</v>
+        <v>0.1403514953863464</v>
       </c>
       <c r="O201" s="2" t="n">
-        <v>0.01265449918109207</v>
+        <v>0.01264927009016013</v>
       </c>
     </row>
     <row r="202">
@@ -13841,28 +13841,28 @@
         <v>250</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>297.9506855347852</v>
+        <v>297.969722100765</v>
       </c>
       <c r="I202" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>125790.3458332463</v>
+        <v>125798.3827881329</v>
       </c>
       <c r="K202" s="2" t="n">
         <v>105546.2799216823</v>
       </c>
       <c r="L202" s="2" t="n">
-        <v>37.00230108501916</v>
+        <v>36.97580030337078</v>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2234.096663543664</v>
+        <v>2234.239403703716</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>0.01350517624974476</v>
+        <v>0.01350603911796836</v>
       </c>
       <c r="O202" s="2" t="n">
-        <v>55.81395256840095</v>
+        <v>55.81751861487187</v>
       </c>
     </row>
     <row r="203">
@@ -13898,28 +13898,28 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>8.64477809204512</v>
+        <v>8.683125522440157</v>
       </c>
       <c r="I203" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>48303.28378463778</v>
+        <v>48517.55265227795</v>
       </c>
       <c r="K203" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L203" s="2" t="n">
-        <v>14.20882213300903</v>
+        <v>14.26071860637735</v>
       </c>
       <c r="M203" s="2" t="n">
-        <v>5.541482512694515</v>
+        <v>5.566064012957247</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>0.07973560416816172</v>
+        <v>0.0800893038812473</v>
       </c>
       <c r="O203" s="2" t="n">
-        <v>5.986156408830897</v>
+        <v>6.012710441077563</v>
       </c>
     </row>
     <row r="204">
@@ -13952,25 +13952,25 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>339.5789253082576</v>
+        <v>341.0867072590226</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>341.2444229520478</v>
+        <v>342.758738601685</v>
       </c>
       <c r="I204" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>44538.3619688306</v>
+        <v>44736.0066305518</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>44320.98541429044</v>
+        <v>44517.77731410319</v>
       </c>
       <c r="L204" s="2" t="n">
-        <v>13.10133832996161</v>
+        <v>13.14921234184258</v>
       </c>
       <c r="M204" s="2" t="n">
-        <v>262.631911533618</v>
+        <v>263.797374137487</v>
       </c>
       <c r="N204" s="2" t="n">
         <v>0</v>
@@ -14012,28 +14012,28 @@
         <v>400</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>500.7261407768431</v>
+        <v>500.729684241985</v>
       </c>
       <c r="I205" s="2" t="n">
         <v>67.79170884624489</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>33945.08074724757</v>
+        <v>33945.32096480479</v>
       </c>
       <c r="K205" s="2" t="n">
         <v>27116.68353849796</v>
       </c>
       <c r="L205" s="2" t="n">
-        <v>9.985234477612586</v>
+        <v>9.977516255851672</v>
       </c>
       <c r="M205" s="2" t="n">
-        <v>11.31533655912466</v>
+        <v>11.31541663383497</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>0.04063158099479209</v>
+        <v>0.04063186853039127</v>
       </c>
       <c r="O205" s="2" t="n">
-        <v>12.04925904132412</v>
+        <v>12.04934430974916</v>
       </c>
     </row>
     <row r="206">
@@ -14069,28 +14069,28 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>10.2028588926216</v>
+        <v>10.24755355177304</v>
       </c>
       <c r="I206" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>16686.70519692657</v>
+        <v>16759.80300304017</v>
       </c>
       <c r="K206" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L206" s="2" t="n">
-        <v>4.908536388254687</v>
+        <v>4.926193129270551</v>
       </c>
       <c r="M206" s="2" t="n">
-        <v>6.287992261230045</v>
+        <v>6.315537449673828</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>0.03192372479357646</v>
+        <v>0.03206356991086267</v>
       </c>
       <c r="O206" s="2" t="n">
-        <v>3.311458096096283</v>
+        <v>3.320504143484384</v>
       </c>
     </row>
     <row r="207">
@@ -14126,28 +14126,28 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>19.61944880384151</v>
+        <v>19.61600877114444</v>
       </c>
       <c r="I207" s="2" t="n">
         <v>751.5482046832743</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>14744.9615254025</v>
+        <v>14742.37617500497</v>
       </c>
       <c r="K207" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L207" s="2" t="n">
-        <v>4.337355957135509</v>
+        <v>4.333212759676092</v>
       </c>
       <c r="M207" s="2" t="n">
-        <v>315.5231378234415</v>
+        <v>315.4678146631608</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>9.646022077287881</v>
+        <v>9.644330764159044</v>
       </c>
       <c r="O207" s="2" t="n">
-        <v>0.4019733181555624</v>
+        <v>0.4019028370033328</v>
       </c>
     </row>
     <row r="208">
@@ -14183,28 +14183,28 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>19.31093156719468</v>
+        <v>19.27576414466844</v>
       </c>
       <c r="I208" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>8611.677988144676</v>
+        <v>8595.995134243234</v>
       </c>
       <c r="K208" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L208" s="2" t="n">
-        <v>2.533198391766738</v>
+        <v>2.526612762803405</v>
       </c>
       <c r="M208" s="2" t="n">
-        <v>200.9858958123369</v>
+        <v>200.6198774307143</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>0.0007707878776328696</v>
+        <v>0.0007693841844512898</v>
       </c>
       <c r="O208" s="2" t="n">
-        <v>3.617442318041586</v>
+        <v>3.610854540439028</v>
       </c>
     </row>
     <row r="209">
@@ -14240,28 +14240,28 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>147.5415534551076</v>
+        <v>147.5202622533353</v>
       </c>
       <c r="I209" s="2" t="n">
         <v>57.55493465680681</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>8491.744468272489</v>
+        <v>8490.519054545719</v>
       </c>
       <c r="K209" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L209" s="2" t="n">
-        <v>2.497918925897554</v>
+        <v>2.495610277928491</v>
       </c>
       <c r="M209" s="2" t="n">
-        <v>7.483459703414258</v>
+        <v>7.482379791709596</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.05006147951831471</v>
+        <v>0.05005425532257809</v>
       </c>
       <c r="O209" s="2" t="n">
-        <v>3.550376647366433</v>
+        <v>3.54986430502086</v>
       </c>
     </row>
     <row r="210">
@@ -14297,28 +14297,28 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>1.645657878099068</v>
+        <v>1.652866849497733</v>
       </c>
       <c r="I210" s="2" t="n">
         <v>4798.899130329469</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>7897.346160029456</v>
+        <v>7931.941286605081</v>
       </c>
       <c r="K210" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L210" s="2" t="n">
-        <v>2.323071603391651</v>
+        <v>2.331428040100676</v>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1.014214163993043</v>
+        <v>1.018657032099257</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.007538092705406986</v>
+        <v>0.007571114085753999</v>
       </c>
       <c r="O210" s="2" t="n">
-        <v>0.9575252486866355</v>
+        <v>0.9601409601115017</v>
       </c>
     </row>
     <row r="211">
@@ -14354,28 +14354,28 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>170.9598218990977</v>
+        <v>169.875157250595</v>
       </c>
       <c r="I211" s="2" t="n">
         <v>43.87420945614248</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>7500.727034585827</v>
+        <v>7453.138230607744</v>
       </c>
       <c r="K211" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L211" s="2" t="n">
-        <v>2.206402711208168</v>
+        <v>2.190693908303305</v>
       </c>
       <c r="M211" s="2" t="n">
-        <v>35.36347300341912</v>
+        <v>35.13910736833014</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>0.00214327848998465</v>
+        <v>0.002129680333504616</v>
       </c>
       <c r="O211" s="2" t="n">
-        <v>4.113903812821031</v>
+        <v>4.087802908038028</v>
       </c>
     </row>
     <row r="212">
@@ -14411,28 +14411,28 @@
         <v>166.6666666666667</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>212.7879955540517</v>
+        <v>212.7963588885685</v>
       </c>
       <c r="I212" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>89835.92537088651</v>
+        <v>89839.45624627046</v>
       </c>
       <c r="K212" s="2" t="n">
         <v>70364.18661445485</v>
       </c>
       <c r="L212" s="2" t="n">
-        <v>43.01258459124678</v>
+        <v>42.99038104161081</v>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1595.528971702769</v>
+        <v>1595.591681737171</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>0.009645016854481674</v>
+        <v>0.009645395938377663</v>
       </c>
       <c r="O212" s="2" t="n">
-        <v>39.86075437169077</v>
+        <v>39.86232104288401</v>
       </c>
     </row>
     <row r="213">
@@ -14468,28 +14468,28 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>4.198820973461658</v>
+        <v>4.215665081311768</v>
       </c>
       <c r="I213" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>23461.19690783486</v>
+        <v>23555.31450263253</v>
       </c>
       <c r="K213" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L213" s="2" t="n">
-        <v>11.2329974054809</v>
+        <v>11.27179513695234</v>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2.691531552415851</v>
+        <v>2.702328975796702</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>0.03872806491366058</v>
+        <v>0.03888342750386264</v>
       </c>
       <c r="O213" s="2" t="n">
-        <v>2.907512351641507</v>
+        <v>2.919176209647389</v>
       </c>
     </row>
     <row r="214">
@@ -14522,25 +14522,25 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>161.7042501467893</v>
+        <v>162.4222415519155</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>165.4153928865426</v>
+        <v>166.080744523857</v>
       </c>
       <c r="I214" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>21589.60014602913</v>
+        <v>21676.44016469642</v>
       </c>
       <c r="K214" s="2" t="n">
-        <v>21105.23114966211</v>
+        <v>21198.94157814438</v>
       </c>
       <c r="L214" s="2" t="n">
-        <v>10.33689471932812</v>
+        <v>10.37270773045959</v>
       </c>
       <c r="M214" s="2" t="n">
-        <v>127.3086324900373</v>
+        <v>127.8207070049502</v>
       </c>
       <c r="N214" s="2" t="n">
         <v>0</v>
@@ -14582,28 +14582,28 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>44.6893252515405</v>
+        <v>44.66787513035706</v>
       </c>
       <c r="I215" s="2" t="n">
         <v>243.170196149393</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>10867.11198720112</v>
+        <v>10861.89595702552</v>
       </c>
       <c r="K215" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L215" s="2" t="n">
-        <v>5.203069614770393</v>
+        <v>5.197683351364272</v>
       </c>
       <c r="M215" s="2" t="n">
-        <v>36.78910444434428</v>
+        <v>36.77144629568977</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>0.04223903758755328</v>
+        <v>0.04221876356305581</v>
       </c>
       <c r="O215" s="2" t="n">
-        <v>5.324800207916045</v>
+        <v>5.322244393768158</v>
       </c>
     </row>
     <row r="216">
@@ -14639,28 +14639,28 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>5.271840557536065</v>
+        <v>5.291291512975024</v>
       </c>
       <c r="I216" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>8622.058792994025</v>
+        <v>8653.870696169828</v>
       </c>
       <c r="K216" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L216" s="2" t="n">
-        <v>4.1281595492369</v>
+        <v>4.141089163466693</v>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3.249020002834503</v>
+        <v>3.261007570099807</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>0.01649506171609441</v>
+        <v>0.01655592180981329</v>
       </c>
       <c r="O216" s="2" t="n">
-        <v>1.711037982521376</v>
+        <v>1.714531698170768</v>
       </c>
     </row>
     <row r="217">
@@ -14696,28 +14696,28 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>15.48998232275669</v>
+        <v>15.47452868215006</v>
       </c>
       <c r="I217" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>6907.731993222132</v>
+        <v>6900.840467757102</v>
       </c>
       <c r="K217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L217" s="2" t="n">
-        <v>3.307356221528023</v>
+        <v>3.302221246787226</v>
       </c>
       <c r="M217" s="2" t="n">
-        <v>161.2179071953898</v>
+        <v>161.0570675284852</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>0.0006182762627262914</v>
+        <v>0.0006176594370281922</v>
       </c>
       <c r="O217" s="2" t="n">
-        <v>2.901678635496105</v>
+        <v>2.898783764614103</v>
       </c>
     </row>
     <row r="218">
@@ -14753,28 +14753,28 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>12.48576788217993</v>
+        <v>12.48740702545687</v>
       </c>
       <c r="I218" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>5669.571941693137</v>
+        <v>5670.316248396503</v>
       </c>
       <c r="K218" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L218" s="2" t="n">
-        <v>2.714536993206784</v>
+        <v>2.713385257773334</v>
       </c>
       <c r="M218" s="2" t="n">
-        <v>80.30171058399692</v>
+        <v>80.31225266761351</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>0.01074688262919086</v>
+        <v>0.01074829348998661</v>
       </c>
       <c r="O218" s="2" t="n">
-        <v>1.113544053291057</v>
+        <v>1.113690240395107</v>
       </c>
     </row>
     <row r="219">
@@ -14810,28 +14810,28 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>4.345122759859251</v>
+        <v>4.344073425133409</v>
       </c>
       <c r="I219" s="2" t="n">
         <v>986.3644347220352</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>4285.87455482642</v>
+        <v>4284.83952837273</v>
       </c>
       <c r="K219" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L219" s="2" t="n">
-        <v>2.052035876247404</v>
+        <v>2.050400700578001</v>
       </c>
       <c r="M219" s="2" t="n">
-        <v>28.15430703025887</v>
+        <v>28.14750784559099</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>0.1299642447289724</v>
+        <v>0.129932858735377</v>
       </c>
       <c r="O219" s="2" t="n">
-        <v>0.01171311234778883</v>
+        <v>0.01171028366463912</v>
       </c>
     </row>
     <row r="220">
@@ -14867,28 +14867,28 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>0.850315194681892</v>
+        <v>0.853452513191494</v>
       </c>
       <c r="I220" s="2" t="n">
         <v>4798.899130329469</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>4080.576848264865</v>
+        <v>4095.63252333216</v>
       </c>
       <c r="K220" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L220" s="2" t="n">
-        <v>1.95374129160978</v>
+        <v>1.959860512755195</v>
       </c>
       <c r="M220" s="2" t="n">
-        <v>0.5240467814009154</v>
+        <v>0.5259803016737143</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>0.003894949765459347</v>
+        <v>0.003909320551809598</v>
       </c>
       <c r="O220" s="2" t="n">
-        <v>0.4947554890268566</v>
+        <v>0.4957657149904493</v>
       </c>
     </row>
     <row r="221">
@@ -14924,28 +14924,28 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>25.9314350653375</v>
+        <v>25.93135052851895</v>
       </c>
       <c r="I221" s="2" t="n">
         <v>149.0342130919736</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>3864.671019308184</v>
+        <v>3864.658420429955</v>
       </c>
       <c r="K221" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L221" s="2" t="n">
-        <v>1.850367639104922</v>
+        <v>1.849333745236806</v>
       </c>
       <c r="M221" s="2" t="n">
-        <v>33.02028455363723</v>
+        <v>33.02017690707634</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>0.01569151900659837</v>
+        <v>0.01569146785204053</v>
       </c>
       <c r="O221" s="2" t="n">
-        <v>0.631413695760359</v>
+        <v>0.6314116373434263</v>
       </c>
     </row>
     <row r="222">
@@ -14981,28 +14981,28 @@
         <v>50</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>86.33381820090872</v>
+        <v>86.34089026749916</v>
       </c>
       <c r="I222" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>36448.85337016297</v>
+        <v>36451.83909144289</v>
       </c>
       <c r="K222" s="2" t="n">
         <v>21109.25598433646</v>
       </c>
       <c r="L222" s="2" t="n">
-        <v>22.56456865791748</v>
+        <v>22.55261728511212</v>
       </c>
       <c r="M222" s="2" t="n">
-        <v>647.3490565978821</v>
+        <v>647.40208443484</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>0.00391324298859709</v>
+        <v>0.003913563543341182</v>
       </c>
       <c r="O222" s="2" t="n">
-        <v>16.1725811285368</v>
+        <v>16.1739059114905</v>
       </c>
     </row>
     <row r="223">
@@ -15038,28 +15038,28 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>3.797146814802257</v>
+        <v>3.811394369511835</v>
       </c>
       <c r="I223" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>21216.81530912911</v>
+        <v>21296.42448718392</v>
       </c>
       <c r="K223" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L223" s="2" t="n">
-        <v>13.13479688601403</v>
+        <v>13.17601863093645</v>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2.434050064480309</v>
+        <v>2.443183043306502</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>0.03502320038406471</v>
+        <v>0.03515461351816616</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>2.629369371738608</v>
+        <v>2.639235222547825</v>
       </c>
     </row>
     <row r="224">
@@ -15092,25 +15092,25 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>145.5338251321104</v>
+        <v>146.180017396724</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>149.4752902220741</v>
+        <v>150.037823725102</v>
       </c>
       <c r="I224" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>19509.1381236793</v>
+        <v>19582.55857861513</v>
       </c>
       <c r="K224" s="2" t="n">
-        <v>18994.7080346959</v>
+        <v>19079.04742032994</v>
       </c>
       <c r="L224" s="2" t="n">
-        <v>12.07761687803648</v>
+        <v>12.11565616700177</v>
       </c>
       <c r="M224" s="2" t="n">
-        <v>115.0406528507048</v>
+        <v>115.4735954550817</v>
       </c>
       <c r="N224" s="2" t="n">
         <v>0</v>
@@ -15152,28 +15152,28 @@
         <v>0</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>63.87149250826143</v>
+        <v>63.85332395062092</v>
       </c>
       <c r="I225" s="2" t="n">
         <v>243.170196149393</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>15531.64336158841</v>
+        <v>15527.22530986322</v>
       </c>
       <c r="K225" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L225" s="2" t="n">
-        <v>9.615249880253858</v>
+        <v>9.606636555005993</v>
       </c>
       <c r="M225" s="2" t="n">
-        <v>52.58023019315073</v>
+        <v>52.56527349016007</v>
       </c>
       <c r="N225" s="2" t="n">
-        <v>0.0603694586491118</v>
+        <v>0.06035228626208717</v>
       </c>
       <c r="O225" s="2" t="n">
-        <v>7.610384239940493</v>
+        <v>7.608219429016247</v>
       </c>
     </row>
     <row r="226">
@@ -15209,28 +15209,28 @@
         <v>0</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>17.67689534863876</v>
+        <v>17.67828979909078</v>
       </c>
       <c r="I226" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>8026.773429604272</v>
+        <v>8027.406625514321</v>
       </c>
       <c r="K226" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L226" s="2" t="n">
-        <v>4.969173606490423</v>
+        <v>4.966526626078983</v>
       </c>
       <c r="M226" s="2" t="n">
-        <v>113.6882366951514</v>
+        <v>113.6972050467721</v>
       </c>
       <c r="N226" s="2" t="n">
-        <v>0.01521504494981392</v>
+        <v>0.01521624519600474</v>
       </c>
       <c r="O226" s="2" t="n">
-        <v>1.576515107590511</v>
+        <v>1.576639471748414</v>
       </c>
     </row>
     <row r="227">
@@ -15266,28 +15266,28 @@
         <v>0</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>4.878875270163989</v>
+        <v>4.895570799588714</v>
       </c>
       <c r="I227" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>7979.36678166518</v>
+        <v>8006.672204640153</v>
       </c>
       <c r="K227" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L227" s="2" t="n">
-        <v>4.939825342735738</v>
+        <v>4.953698316993385</v>
       </c>
       <c r="M227" s="2" t="n">
-        <v>3.006836639138806</v>
+        <v>3.017126045365499</v>
       </c>
       <c r="N227" s="2" t="n">
-        <v>0.01526551264367052</v>
+        <v>0.01531775128504028</v>
       </c>
       <c r="O227" s="2" t="n">
-        <v>1.58349646733938</v>
+        <v>1.586306726051985</v>
       </c>
     </row>
     <row r="228">
@@ -15323,28 +15323,28 @@
         <v>0</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>17.4572882599977</v>
+        <v>17.44422534697549</v>
       </c>
       <c r="I228" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>7785.048821606807</v>
+        <v>7779.223437153292</v>
       </c>
       <c r="K228" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L228" s="2" t="n">
-        <v>4.819527979560168</v>
+        <v>4.812976610408605</v>
       </c>
       <c r="M228" s="2" t="n">
-        <v>181.6933951208412</v>
+        <v>181.5574378643747</v>
       </c>
       <c r="N228" s="2" t="n">
-        <v>0.0006968004687048653</v>
+        <v>0.000696279067913347</v>
       </c>
       <c r="O228" s="2" t="n">
-        <v>3.270206467783584</v>
+        <v>3.267759442677673</v>
       </c>
     </row>
     <row r="229">
@@ -15380,28 +15380,28 @@
         <v>0</v>
       </c>
       <c r="H229" s="2" t="n">
-        <v>37.42093929824042</v>
+        <v>37.4208698622743</v>
       </c>
       <c r="I229" s="2" t="n">
         <v>149.0342130919736</v>
       </c>
       <c r="J229" s="2" t="n">
-        <v>5577.00024147577</v>
+        <v>5576.989893141199</v>
       </c>
       <c r="K229" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L229" s="2" t="n">
-        <v>3.452580622385699</v>
+        <v>3.45046290661581</v>
       </c>
       <c r="M229" s="2" t="n">
-        <v>47.6506626331674</v>
+        <v>47.6505742155633</v>
       </c>
       <c r="N229" s="2" t="n">
-        <v>0.02264399863577165</v>
+        <v>0.02264395661897699</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>0.9111757032185875</v>
+        <v>0.9111740124976584</v>
       </c>
     </row>
     <row r="230">
@@ -15437,28 +15437,28 @@
         <v>0</v>
       </c>
       <c r="H230" s="2" t="n">
-        <v>5.592060325122636</v>
+        <v>5.591172761517473</v>
       </c>
       <c r="I230" s="2" t="n">
         <v>986.3644347220352</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>5515.809421521109</v>
+        <v>5514.933960347423</v>
       </c>
       <c r="K230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L230" s="2" t="n">
-        <v>3.41469892432297</v>
+        <v>3.412069131776141</v>
       </c>
       <c r="M230" s="2" t="n">
-        <v>36.2338631211266</v>
+        <v>36.22811213556653</v>
       </c>
       <c r="N230" s="2" t="n">
-        <v>0.1672606130596312</v>
+        <v>0.1672340657006798</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>0.01507447187657724</v>
+        <v>0.01507207927853165</v>
       </c>
     </row>
     <row r="231">
@@ -15494,28 +15494,28 @@
         <v>0</v>
       </c>
       <c r="H231" s="2" t="n">
-        <v>1.289890874962143</v>
+        <v>1.289774238573964</v>
       </c>
       <c r="I231" s="2" t="n">
         <v>2963.345789569951</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>3822.392693323765</v>
+        <v>3822.047059373946</v>
       </c>
       <c r="K231" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L231" s="2" t="n">
-        <v>2.366347206867994</v>
+        <v>2.364686301821838</v>
       </c>
       <c r="M231" s="2" t="n">
-        <v>29.60384907835741</v>
+        <v>29.60117219607247</v>
       </c>
       <c r="N231" s="2" t="n">
-        <v>0.6548135479847663</v>
+        <v>0.6547543374820409</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>0.02642794505855766</v>
+        <v>0.02642555535248372</v>
       </c>
     </row>
     <row r="232">
@@ -15551,28 +15551,28 @@
         <v>150</v>
       </c>
       <c r="H232" s="2" t="n">
-        <v>192.6178018542324</v>
+        <v>192.64169441125</v>
       </c>
       <c r="I232" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>81320.3697296238</v>
+        <v>81330.45681166789</v>
       </c>
       <c r="K232" s="2" t="n">
         <v>63327.76795300938</v>
       </c>
       <c r="L232" s="2" t="n">
-        <v>28.14999346153587</v>
+        <v>28.12154374660508</v>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1444.288633500779</v>
+        <v>1444.467784899007</v>
       </c>
       <c r="N232" s="2" t="n">
-        <v>0.008730764818381732</v>
+        <v>0.008731847793549253</v>
       </c>
       <c r="O232" s="2" t="n">
-        <v>36.08234979297151</v>
+        <v>36.08682549351144</v>
       </c>
     </row>
     <row r="233">
@@ -15608,28 +15608,28 @@
         <v>0</v>
       </c>
       <c r="H233" s="2" t="n">
-        <v>11.13130161496497</v>
+        <v>11.17940094139434</v>
       </c>
       <c r="I233" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>62196.90257807992</v>
+        <v>62465.66082608001</v>
       </c>
       <c r="K233" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L233" s="2" t="n">
-        <v>21.53018249575085</v>
+        <v>21.59868372126484</v>
       </c>
       <c r="M233" s="2" t="n">
-        <v>7.135395794556928</v>
+        <v>7.16622846295428</v>
       </c>
       <c r="N233" s="2" t="n">
-        <v>0.1026701958103465</v>
+        <v>0.1031138426931342</v>
       </c>
       <c r="O233" s="2" t="n">
-        <v>7.707972580854132</v>
+        <v>7.741279403551009</v>
       </c>
     </row>
     <row r="234">
@@ -15662,25 +15662,25 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>436.6014753963312</v>
+        <v>438.5400521901719</v>
       </c>
       <c r="H234" s="2" t="n">
-        <v>439.3793749823446</v>
+        <v>441.2806333000996</v>
       </c>
       <c r="I234" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J234" s="2" t="n">
-        <v>57346.68855629068</v>
+        <v>57594.83599975621</v>
       </c>
       <c r="K234" s="2" t="n">
-        <v>56984.12410408771</v>
+        <v>57237.14226098981</v>
       </c>
       <c r="L234" s="2" t="n">
-        <v>19.85122440131071</v>
+        <v>19.91450390960216</v>
       </c>
       <c r="M234" s="2" t="n">
-        <v>338.1595049724079</v>
+        <v>339.6227702237241</v>
       </c>
       <c r="N234" s="2" t="n">
         <v>0</v>
@@ -15722,28 +15722,28 @@
         <v>0</v>
       </c>
       <c r="H235" s="2" t="n">
-        <v>13.15503538899192</v>
+        <v>13.20932159635034</v>
       </c>
       <c r="I235" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>21514.9694513555</v>
+        <v>21603.75416826502</v>
       </c>
       <c r="K235" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L235" s="2" t="n">
-        <v>7.447657350728614</v>
+        <v>7.469906622319729</v>
       </c>
       <c r="M235" s="2" t="n">
-        <v>8.107410049746774</v>
+        <v>8.140866481454179</v>
       </c>
       <c r="N235" s="2" t="n">
-        <v>0.04116078971861877</v>
+        <v>0.04133064583071795</v>
       </c>
       <c r="O235" s="2" t="n">
-        <v>4.269621769915235</v>
+        <v>4.280202769539087</v>
       </c>
     </row>
     <row r="236">
@@ -15779,28 +15779,28 @@
         <v>0</v>
       </c>
       <c r="H236" s="2" t="n">
-        <v>2.1218256424405</v>
+        <v>2.13058167109401</v>
       </c>
       <c r="I236" s="2" t="n">
         <v>4798.899130329469</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>10182.42723021848</v>
+        <v>10224.44652850895</v>
       </c>
       <c r="K236" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L236" s="2" t="n">
-        <v>3.524765823203066</v>
+        <v>3.535295774891546</v>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1.307674972256442</v>
+        <v>1.31307128724931</v>
       </c>
       <c r="N236" s="2" t="n">
-        <v>0.009719224518222349</v>
+        <v>0.009759332341725494</v>
       </c>
       <c r="O236" s="2" t="n">
-        <v>1.234583234453554</v>
+        <v>1.237642785262344</v>
       </c>
     </row>
     <row r="237">
@@ -15836,28 +15836,28 @@
         <v>0</v>
       </c>
       <c r="H237" s="2" t="n">
-        <v>32.25272777720835</v>
+        <v>32.19160514001714</v>
       </c>
       <c r="I237" s="2" t="n">
         <v>243.170196149393</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>7842.902139936728</v>
+        <v>7828.038936261773</v>
       </c>
       <c r="K237" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L237" s="2" t="n">
-        <v>2.714911954934934</v>
+        <v>2.706692523638106</v>
       </c>
       <c r="M237" s="2" t="n">
-        <v>26.5510603288829</v>
+        <v>26.50074300878723</v>
       </c>
       <c r="N237" s="2" t="n">
-        <v>0.03048433094960784</v>
+        <v>0.03042655962826346</v>
       </c>
       <c r="O237" s="2" t="n">
-        <v>3.842960944415211</v>
+        <v>3.835678090413898</v>
       </c>
     </row>
     <row r="238">
@@ -15893,28 +15893,28 @@
         <v>0</v>
       </c>
       <c r="H238" s="2" t="n">
-        <v>14.98594333392515</v>
+        <v>14.94177049793229</v>
       </c>
       <c r="I238" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>6682.956639936688</v>
+        <v>6663.257836796609</v>
       </c>
       <c r="K238" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L238" s="2" t="n">
-        <v>2.313383305356693</v>
+        <v>2.303947427546021</v>
       </c>
       <c r="M238" s="2" t="n">
-        <v>155.9719289088349</v>
+        <v>155.5121832470731</v>
       </c>
       <c r="N238" s="2" t="n">
-        <v>0.000598157754145086</v>
+        <v>0.0005963946135951082</v>
       </c>
       <c r="O238" s="2" t="n">
-        <v>2.807258956062331</v>
+        <v>2.798984229093697</v>
       </c>
     </row>
     <row r="239">
@@ -15950,28 +15950,28 @@
         <v>0</v>
       </c>
       <c r="H239" s="2" t="n">
-        <v>4.871293404419699</v>
+        <v>4.891395520152301</v>
       </c>
       <c r="I239" s="2" t="n">
         <v>924.0344320034608</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>4501.242834075161</v>
+        <v>4519.817881168204</v>
       </c>
       <c r="K239" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L239" s="2" t="n">
-        <v>1.558157651880946</v>
+        <v>1.562812521344707</v>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3.00216395733192</v>
+        <v>3.014552832792342</v>
       </c>
       <c r="N239" s="2" t="n">
-        <v>0.004490826205655497</v>
+        <v>0.004509358266984257</v>
       </c>
       <c r="O239" s="2" t="n">
-        <v>0.627100818371348</v>
+        <v>0.6421510107050549</v>
       </c>
     </row>
     <row r="240">
@@ -16007,28 +16007,28 @@
         <v>0</v>
       </c>
       <c r="H240" s="2" t="n">
-        <v>9.690896887692922</v>
+        <v>9.695536246453548</v>
       </c>
       <c r="I240" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>4400.469206441185</v>
+        <v>4402.575859272223</v>
       </c>
       <c r="K240" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L240" s="2" t="n">
-        <v>1.523273686542083</v>
+        <v>1.522273874730156</v>
       </c>
       <c r="M240" s="2" t="n">
-        <v>62.32661094761647</v>
+        <v>62.35644879563724</v>
       </c>
       <c r="N240" s="2" t="n">
-        <v>0.008341251607942234</v>
+        <v>0.008345244846047062</v>
       </c>
       <c r="O240" s="2" t="n">
-        <v>0.864283294562031</v>
+        <v>0.8646970560869711</v>
       </c>
     </row>
     <row r="241">
@@ -16064,28 +16064,28 @@
         <v>0</v>
       </c>
       <c r="H241" s="2" t="n">
-        <v>3.569293241785101</v>
+        <v>3.566296732901693</v>
       </c>
       <c r="I241" s="2" t="n">
         <v>986.3644347220352</v>
       </c>
       <c r="J241" s="2" t="n">
-        <v>3520.623910790542</v>
+        <v>3517.66826099962</v>
       </c>
       <c r="K241" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L241" s="2" t="n">
-        <v>1.218704986201974</v>
+        <v>1.216300335270628</v>
       </c>
       <c r="M241" s="2" t="n">
-        <v>23.12730465030656</v>
+        <v>23.10788871299365</v>
       </c>
       <c r="N241" s="2" t="n">
-        <v>0.1067588940570812</v>
+        <v>0.1066692673571284</v>
       </c>
       <c r="O241" s="2" t="n">
-        <v>0.009621714978793036</v>
+        <v>0.009613637313985325</v>
       </c>
     </row>
     <row r="242">
@@ -16121,28 +16121,28 @@
         <v>0</v>
       </c>
       <c r="H242" s="2" t="n">
-        <v>12.35526416708475</v>
+        <v>12.40880651769103</v>
       </c>
       <c r="I242" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>69035.8763339493</v>
+        <v>69335.04784862489</v>
       </c>
       <c r="K242" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L242" s="2" t="n">
-        <v>24.55492116944038</v>
+        <v>24.62931233245403</v>
       </c>
       <c r="M242" s="2" t="n">
-        <v>7.919981241001874</v>
+        <v>7.954303001076461</v>
       </c>
       <c r="N242" s="2" t="n">
-        <v>0.1139594842725085</v>
+        <v>0.1144533351994749</v>
       </c>
       <c r="O242" s="2" t="n">
-        <v>8.555516751164639</v>
+        <v>8.592592646209365</v>
       </c>
     </row>
     <row r="243">
@@ -16175,25 +16175,25 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>485.1127504403681</v>
+        <v>487.2667246557466</v>
       </c>
       <c r="H243" s="2" t="n">
-        <v>487.7456508761415</v>
+        <v>489.8619617712763</v>
       </c>
       <c r="I243" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>63659.33297757388</v>
+        <v>63935.54854139377</v>
       </c>
       <c r="K243" s="2" t="n">
-        <v>63315.69344898634</v>
+        <v>63596.82473443313</v>
       </c>
       <c r="L243" s="2" t="n">
-        <v>22.64257348457505</v>
+        <v>22.71129310548234</v>
       </c>
       <c r="M243" s="2" t="n">
-        <v>375.3836371116611</v>
+        <v>377.0124132568665</v>
       </c>
       <c r="N243" s="2" t="n">
         <v>0</v>
@@ -16235,28 +16235,28 @@
         <v>100</v>
       </c>
       <c r="H244" s="2" t="n">
-        <v>137.2011814805265</v>
+        <v>137.2277769797463</v>
       </c>
       <c r="I244" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J244" s="2" t="n">
-        <v>57924.29722451672</v>
+        <v>57935.52544853797</v>
       </c>
       <c r="K244" s="2" t="n">
         <v>42218.51196867292</v>
       </c>
       <c r="L244" s="2" t="n">
-        <v>20.60271597427082</v>
+        <v>20.5799548091778</v>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1028.763203648032</v>
+        <v>1028.962622273183</v>
       </c>
       <c r="N244" s="2" t="n">
-        <v>0.006218902078516617</v>
+        <v>0.006220107569632602</v>
       </c>
       <c r="O244" s="2" t="n">
-        <v>25.70136806947755</v>
+        <v>25.70635010175354</v>
       </c>
     </row>
     <row r="245">
@@ -16292,28 +16292,28 @@
         <v>0</v>
       </c>
       <c r="H245" s="2" t="n">
-        <v>14.55009252608375</v>
+        <v>14.61061599889555</v>
       </c>
       <c r="I245" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J245" s="2" t="n">
-        <v>23796.57575646223</v>
+        <v>23895.5614779089</v>
       </c>
       <c r="K245" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L245" s="2" t="n">
-        <v>8.464049025407933</v>
+        <v>8.488221545381789</v>
       </c>
       <c r="M245" s="2" t="n">
-        <v>8.967179705911565</v>
+        <v>9.004480146177244</v>
       </c>
       <c r="N245" s="2" t="n">
-        <v>0.04552578394078143</v>
+        <v>0.04571515583251588</v>
       </c>
       <c r="O245" s="2" t="n">
-        <v>4.722404004753399</v>
+        <v>4.734262740671198</v>
       </c>
     </row>
     <row r="246">
@@ -16349,28 +16349,28 @@
         <v>0</v>
       </c>
       <c r="H246" s="2" t="n">
-        <v>2.34683970881299</v>
+        <v>2.35660176971091</v>
       </c>
       <c r="I246" s="2" t="n">
         <v>4798.899130329469</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>11262.24703764532</v>
+        <v>11309.09418319857</v>
       </c>
       <c r="K246" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L246" s="2" t="n">
-        <v>4.005795289139399</v>
+        <v>4.017235459954483</v>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1.446350486924328</v>
+        <v>1.452366816663453</v>
       </c>
       <c r="N246" s="2" t="n">
-        <v>0.01074992288810207</v>
+        <v>0.01079463893815334</v>
       </c>
       <c r="O246" s="2" t="n">
-        <v>1.365507561270612</v>
+        <v>1.368936576142397</v>
       </c>
     </row>
     <row r="247">
@@ -16406,28 +16406,28 @@
         <v>0</v>
       </c>
       <c r="H247" s="2" t="n">
-        <v>32.17051207112068</v>
+        <v>32.1024629734608</v>
       </c>
       <c r="I247" s="2" t="n">
         <v>243.170196149393</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>7822.90973056083</v>
+        <v>7806.362218135087</v>
       </c>
       <c r="K247" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L247" s="2" t="n">
-        <v>2.782479805432788</v>
+        <v>2.772989119016391</v>
       </c>
       <c r="M247" s="2" t="n">
-        <v>26.48337879238174</v>
+        <v>26.42735947799152</v>
       </c>
       <c r="N247" s="2" t="n">
-        <v>0.03040662307910012</v>
+        <v>0.03034230507076868</v>
       </c>
       <c r="O247" s="2" t="n">
-        <v>3.833164819582145</v>
+        <v>3.825056667415418</v>
       </c>
     </row>
     <row r="248">
@@ -16463,28 +16463,28 @@
         <v>0</v>
       </c>
       <c r="H248" s="2" t="n">
-        <v>14.68145089899588</v>
+        <v>14.6322826684658</v>
       </c>
       <c r="I248" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J248" s="2" t="n">
-        <v>6547.168742272986</v>
+        <v>6525.242251202444</v>
       </c>
       <c r="K248" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L248" s="2" t="n">
-        <v>2.328719803191357</v>
+        <v>2.317907529257987</v>
       </c>
       <c r="M248" s="2" t="n">
-        <v>152.8028075958941</v>
+        <v>152.2910704575685</v>
       </c>
       <c r="N248" s="2" t="n">
-        <v>0.0005860040640521077</v>
+        <v>0.0005840415343872194</v>
       </c>
       <c r="O248" s="2" t="n">
-        <v>2.750219562814837</v>
+        <v>2.741009067857416</v>
       </c>
     </row>
     <row r="249">
@@ -16520,28 +16520,28 @@
         <v>0</v>
       </c>
       <c r="H249" s="2" t="n">
-        <v>5.387881344303972</v>
+        <v>5.410293111752912</v>
       </c>
       <c r="I249" s="2" t="n">
         <v>924.0344320034608</v>
       </c>
       <c r="J249" s="2" t="n">
-        <v>4978.587877685964</v>
+        <v>4999.297122490839</v>
       </c>
       <c r="K249" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L249" s="2" t="n">
-        <v>1.77080149284051</v>
+        <v>1.775858733686697</v>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3.320535602223153</v>
+        <v>3.334347909318896</v>
       </c>
       <c r="N249" s="2" t="n">
-        <v>0.004967066593034553</v>
+        <v>0.004987727913184852</v>
       </c>
       <c r="O249" s="2" t="n">
-        <v>0.6936032219359282</v>
+        <v>0.7102727995740884</v>
       </c>
     </row>
     <row r="250">
@@ -16577,28 +16577,28 @@
         <v>0</v>
       </c>
       <c r="H250" s="2" t="n">
-        <v>9.913121614392164</v>
+        <v>9.918289065916879</v>
       </c>
       <c r="I250" s="2" t="n">
         <v>454.0827600827758</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>4501.377623699416</v>
+        <v>4503.724074350353</v>
       </c>
       <c r="K250" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L250" s="2" t="n">
-        <v>1.601065686037608</v>
+        <v>1.59982044187148</v>
       </c>
       <c r="M250" s="2" t="n">
-        <v>63.75584027947673</v>
+        <v>63.7890745347272</v>
       </c>
       <c r="N250" s="2" t="n">
-        <v>0.008532527232931972</v>
+        <v>0.008536975016644771</v>
       </c>
       <c r="O250" s="2" t="n">
-        <v>0.8841024218472138</v>
+        <v>0.884563281361047</v>
       </c>
     </row>
     <row r="251">
@@ -16634,28 +16634,28 @@
         <v>0</v>
       </c>
       <c r="H251" s="2" t="n">
-        <v>3.5316256818239</v>
+        <v>3.528290086937671</v>
       </c>
       <c r="I251" s="2" t="n">
         <v>986.3644347220352</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>3483.469969302054</v>
+        <v>3480.179857137636</v>
       </c>
       <c r="K251" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L251" s="2" t="n">
-        <v>1.23901274286079</v>
+        <v>1.236235343223435</v>
       </c>
       <c r="M251" s="2" t="n">
-        <v>22.88323696641386</v>
+        <v>22.86162391478203</v>
       </c>
       <c r="N251" s="2" t="n">
-        <v>0.1056322432691299</v>
+        <v>0.105532474380178</v>
       </c>
       <c r="O251" s="2" t="n">
-        <v>0.009520174841476662</v>
+        <v>0.00951118310526841</v>
       </c>
     </row>
     <row r="252">
@@ -16691,28 +16691,28 @@
         <v>333.3333333333333</v>
       </c>
       <c r="H252" s="2" t="n">
-        <v>390.5272868483686</v>
+        <v>390.5454283957022</v>
       </c>
       <c r="I252" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J252" s="2" t="n">
-        <v>164874.8093390121</v>
+        <v>164882.4684303445</v>
       </c>
       <c r="K252" s="2" t="n">
         <v>140728.3732289097</v>
       </c>
       <c r="L252" s="2" t="n">
-        <v>45.0029435376573</v>
+        <v>44.97406643675875</v>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2928.255415840752</v>
+        <v>2928.39144496348</v>
       </c>
       <c r="N252" s="2" t="n">
-        <v>0.01770138514618756</v>
+        <v>0.01770220744600453</v>
       </c>
       <c r="O252" s="2" t="n">
-        <v>73.15597017573033</v>
+        <v>73.15936856181082</v>
       </c>
     </row>
     <row r="253">
@@ -16748,28 +16748,28 @@
         <v>0</v>
       </c>
       <c r="H253" s="2" t="n">
-        <v>8.241656249167219</v>
+        <v>8.278196874098558</v>
       </c>
       <c r="I253" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J253" s="2" t="n">
-        <v>46050.81315219488</v>
+        <v>46254.98637178864</v>
       </c>
       <c r="K253" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L253" s="2" t="n">
-        <v>12.56967120968832</v>
+        <v>12.61671328625831</v>
       </c>
       <c r="M253" s="2" t="n">
-        <v>5.283073029072408</v>
+        <v>5.306496329462997</v>
       </c>
       <c r="N253" s="2" t="n">
-        <v>0.076017386840544</v>
+        <v>0.07635442138030432</v>
       </c>
       <c r="O253" s="2" t="n">
-        <v>5.707010966624133</v>
+        <v>5.732313859744861</v>
       </c>
     </row>
     <row r="254">
@@ -16802,25 +16802,25 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>323.4085002935786</v>
+        <v>324.844483103831</v>
       </c>
       <c r="H254" s="2" t="n">
-        <v>325.3073946621051</v>
+        <v>326.7505985769597</v>
       </c>
       <c r="I254" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>42458.30120609483</v>
+        <v>42646.66454343108</v>
       </c>
       <c r="K254" s="2" t="n">
-        <v>42210.46229932422</v>
+        <v>42397.88315628875</v>
       </c>
       <c r="L254" s="2" t="n">
-        <v>11.58908713552409</v>
+        <v>11.6324915725816</v>
       </c>
       <c r="M254" s="2" t="n">
-        <v>250.3662980248481</v>
+        <v>251.4770309112998</v>
       </c>
       <c r="N254" s="2" t="n">
         <v>0</v>
@@ -16862,28 +16862,28 @@
         <v>333.3333333333333</v>
       </c>
       <c r="H255" s="2" t="n">
-        <v>436.4818072437415</v>
+        <v>436.4851806648663</v>
       </c>
       <c r="I255" s="2" t="n">
         <v>67.79170884624489</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>29589.8475933505</v>
+        <v>29590.07628333321</v>
       </c>
       <c r="K255" s="2" t="n">
         <v>22597.23628208162</v>
       </c>
       <c r="L255" s="2" t="n">
-        <v>8.07661428613614</v>
+        <v>8.071119199659396</v>
       </c>
       <c r="M255" s="2" t="n">
-        <v>9.86355244652392</v>
+        <v>9.863628678604243</v>
       </c>
       <c r="N255" s="2" t="n">
-        <v>0.03541845423980208</v>
+        <v>0.03541872797712573</v>
       </c>
       <c r="O255" s="2" t="n">
-        <v>10.50331095985067</v>
+        <v>10.50339213640943</v>
       </c>
     </row>
     <row r="256">
@@ -16919,28 +16919,28 @@
         <v>0</v>
       </c>
       <c r="H256" s="2" t="n">
-        <v>9.750313502197505</v>
+        <v>9.792673708488632</v>
       </c>
       <c r="I256" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>15946.57033887263</v>
+        <v>16015.85016346887</v>
       </c>
       <c r="K256" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L256" s="2" t="n">
-        <v>4.352651611587093</v>
+        <v>4.368553650064479</v>
       </c>
       <c r="M256" s="2" t="n">
-        <v>6.009089853307901</v>
+        <v>6.035196325243462</v>
       </c>
       <c r="N256" s="2" t="n">
-        <v>0.03050775553902292</v>
+        <v>0.03064029638684499</v>
       </c>
       <c r="O256" s="2" t="n">
-        <v>3.164579156306706</v>
+        <v>3.173109899894208</v>
       </c>
     </row>
     <row r="257">
@@ -16976,28 +16976,28 @@
         <v>0</v>
       </c>
       <c r="H257" s="2" t="n">
-        <v>17.99051162474849</v>
+        <v>17.98723320119033</v>
       </c>
       <c r="I257" s="2" t="n">
         <v>751.5482046832743</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>13520.7367129133</v>
+        <v>13518.27281957398</v>
       </c>
       <c r="K257" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L257" s="2" t="n">
-        <v>3.690514962947665</v>
+        <v>3.687303481598416</v>
       </c>
       <c r="M257" s="2" t="n">
-        <v>289.3263075656994</v>
+        <v>289.2735834296379</v>
       </c>
       <c r="N257" s="2" t="n">
-        <v>8.845145143937453</v>
+        <v>8.843533286930821</v>
       </c>
       <c r="O257" s="2" t="n">
-        <v>0.3685988187242239</v>
+        <v>0.3685316487028248</v>
       </c>
     </row>
     <row r="258">
@@ -17033,28 +17033,28 @@
         <v>0</v>
       </c>
       <c r="H258" s="2" t="n">
-        <v>146.598161471802</v>
+        <v>146.5778196812588</v>
       </c>
       <c r="I258" s="2" t="n">
         <v>57.55493465680681</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>8437.447604317578</v>
+        <v>8436.27683389206</v>
       </c>
       <c r="K258" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L258" s="2" t="n">
-        <v>2.303019968067372</v>
+        <v>2.301115930749398</v>
       </c>
       <c r="M258" s="2" t="n">
-        <v>7.435609889404135</v>
+        <v>7.434578132815831</v>
       </c>
       <c r="N258" s="2" t="n">
-        <v>0.04974138258735507</v>
+        <v>0.04973448053090521</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>3.527675267393096</v>
+        <v>3.527185771272042</v>
       </c>
     </row>
     <row r="259">
@@ -17090,28 +17090,28 @@
         <v>0</v>
       </c>
       <c r="H259" s="2" t="n">
-        <v>18.80452079204806</v>
+        <v>18.77100233014283</v>
       </c>
       <c r="I259" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J259" s="2" t="n">
-        <v>8385.844940675441</v>
+        <v>8370.897438035221</v>
       </c>
       <c r="K259" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L259" s="2" t="n">
-        <v>2.288934906998372</v>
+        <v>2.283282759516261</v>
       </c>
       <c r="M259" s="2" t="n">
-        <v>195.7152322538388</v>
+        <v>195.3663760596758</v>
       </c>
       <c r="N259" s="2" t="n">
-        <v>0.0007505747001780448</v>
+        <v>0.0007492368245803011</v>
       </c>
       <c r="O259" s="2" t="n">
-        <v>3.522578341026636</v>
+        <v>3.516299456856303</v>
       </c>
     </row>
     <row r="260">
@@ -17147,28 +17147,28 @@
         <v>0</v>
       </c>
       <c r="H260" s="2" t="n">
-        <v>1.572665112562793</v>
+        <v>1.57949755118951</v>
       </c>
       <c r="I260" s="2" t="n">
         <v>4798.899130329469</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>7547.061240977082</v>
+        <v>7579.849424760867</v>
       </c>
       <c r="K260" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L260" s="2" t="n">
-        <v>2.059987042681414</v>
+        <v>2.067513028250402</v>
       </c>
       <c r="M260" s="2" t="n">
-        <v>0.9692289348873265</v>
+        <v>0.9734397469413087</v>
       </c>
       <c r="N260" s="2" t="n">
-        <v>0.007203742388272992</v>
+        <v>0.007235039024382859</v>
       </c>
       <c r="O260" s="2" t="n">
-        <v>0.915054442996949</v>
+        <v>0.9175211516606451</v>
       </c>
     </row>
     <row r="261">
@@ -17204,28 +17204,28 @@
         <v>0</v>
       </c>
       <c r="H261" s="2" t="n">
-        <v>154.5233649100178</v>
+        <v>153.4903994507764</v>
       </c>
       <c r="I261" s="2" t="n">
         <v>43.87420945614248</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>6779.59047793006</v>
+        <v>6734.269935010341</v>
       </c>
       <c r="K261" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L261" s="2" t="n">
-        <v>1.85050420200567</v>
+        <v>1.836869051897839</v>
       </c>
       <c r="M261" s="2" t="n">
-        <v>31.96355016454154</v>
+        <v>31.74987863794795</v>
       </c>
       <c r="N261" s="2" t="n">
-        <v>0.001937218935611432</v>
+        <v>0.001924268918320258</v>
       </c>
       <c r="O261" s="2" t="n">
-        <v>3.71838396303695</v>
+        <v>3.6935271253655</v>
       </c>
     </row>
     <row r="262">
@@ -17261,28 +17261,28 @@
         <v>200</v>
       </c>
       <c r="H262" s="2" t="n">
-        <v>242.8574161971897</v>
+        <v>242.8845705329081</v>
       </c>
       <c r="I262" s="2" t="n">
         <v>422.1851196867292</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>102530.7873240203</v>
+        <v>102542.2514804956</v>
       </c>
       <c r="K262" s="2" t="n">
         <v>84437.02393734583</v>
       </c>
       <c r="L262" s="2" t="n">
-        <v>29.0865006935346</v>
+        <v>29.05871195694003</v>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1820.995787504683</v>
+        <v>1821.199396402983</v>
       </c>
       <c r="N262" s="2" t="n">
-        <v>0.01100797000488106</v>
+        <v>0.01100920082631436</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>45.49354294716617</v>
+        <v>45.49862966412771</v>
       </c>
     </row>
     <row r="263">
@@ -17318,28 +17318,28 @@
         <v>0</v>
       </c>
       <c r="H263" s="2" t="n">
-        <v>12.3239642601475</v>
+        <v>12.37865206696616</v>
       </c>
       <c r="I263" s="2" t="n">
         <v>5587.567809182541</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>68860.98598151629</v>
+        <v>69166.55781045106</v>
       </c>
       <c r="K263" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L263" s="2" t="n">
-        <v>19.53486527104446</v>
+        <v>19.60061390742172</v>
       </c>
       <c r="M263" s="2" t="n">
-        <v>7.899917349818667</v>
+        <v>7.934973371143507</v>
       </c>
       <c r="N263" s="2" t="n">
-        <v>0.1136707877943021</v>
+        <v>0.1141752039020251</v>
       </c>
       <c r="O263" s="2" t="n">
-        <v>8.533842841607532</v>
+        <v>8.571711918382759</v>
       </c>
     </row>
     <row r="264">
@@ -17372,25 +17372,25 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>485.1127504403681</v>
+        <v>487.2667246557466</v>
       </c>
       <c r="H264" s="2" t="n">
-        <v>486.620846145423</v>
+        <v>488.7811782137155</v>
       </c>
       <c r="I264" s="2" t="n">
         <v>130.5174794756695</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>63512.5262992182</v>
+        <v>63794.48739560219</v>
       </c>
       <c r="K264" s="2" t="n">
-        <v>63315.69344898634</v>
+        <v>63596.82473443313</v>
       </c>
       <c r="L264" s="2" t="n">
-        <v>18.01758465398574</v>
+        <v>18.07826146690421</v>
       </c>
       <c r="M264" s="2" t="n">
-        <v>374.5179537578494</v>
+        <v>376.1806099142044</v>
       </c>
       <c r="N264" s="2" t="n">
         <v>0</v>
@@ -17432,28 +17432,28 @@
         <v>300</v>
       </c>
       <c r="H265" s="2" t="n">
-        <v>379.848254953457</v>
+        <v>379.8532986639671</v>
       </c>
       <c r="I265" s="2" t="n">
         <v>67.79170884624489</v>
       </c>
       <c r="J265" s="2" t="n">
-        <v>25750.56230555895</v>
+        <v>25750.90422731336</v>
       </c>
       <c r="K265" s="2" t="n">
         <v>20337.51265387347</v>
       </c>
       <c r="L265" s="2" t="n">
-        <v>7.305061902943921</v>
+        <v>7.297363747806716</v>
       </c>
       <c r="M265" s="2" t="n">
-        <v>8.583755662379293</v>
+        <v>8.583869639416402</v>
       </c>
       <c r="N265" s="2" t="n">
-        <v>0.03082290673486162</v>
+        <v>0.0308233160083455</v>
       </c>
       <c r="O265" s="2" t="n">
-        <v>9.140505453197218</v>
+        <v>9.140626822883192</v>
       </c>
     </row>
     <row r="266">
@@ -17489,28 +17489,28 @@
         <v>0</v>
       </c>
       <c r="H266" s="2" t="n">
-        <v>14.40674078680686</v>
+        <v>14.46976419575466</v>
       </c>
       <c r="I266" s="2" t="n">
         <v>1635.493088020055</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>23562.12497771922</v>
+        <v>23665.19932743681</v>
       </c>
       <c r="K266" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L266" s="2" t="n">
-        <v>6.684233900786809</v>
+        <v>6.706310820475396</v>
       </c>
       <c r="M266" s="2" t="n">
-        <v>8.878832445923599</v>
+        <v>8.917673589559007</v>
       </c>
       <c r="N266" s="2" t="n">
-        <v>0.04507725068931546</v>
+        <v>0.04527444463112892</v>
       </c>
       <c r="O266" s="2" t="n">
-        <v>4.675877508345491</v>
+        <v>4.688622677061512</v>
       </c>
     </row>
     <row r="267">
@@ -17546,28 +17546,28 @@
         <v>0</v>
       </c>
       <c r="H267" s="2" t="n">
-        <v>15.33803161601061</v>
+        <v>15.33312425216871</v>
       </c>
       <c r="I267" s="2" t="n">
         <v>751.5482046832743</v>
       </c>
       <c r="J267" s="2" t="n">
-        <v>11527.27012438807</v>
+        <v>11523.58200390296</v>
       </c>
       <c r="K267" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L267" s="2" t="n">
-        <v>3.270119729091606</v>
+        <v>3.265585115685579</v>
       </c>
       <c r="M267" s="2" t="n">
-        <v>246.6686965523332</v>
+        <v>246.5897755360845</v>
       </c>
       <c r="N267" s="2" t="n">
-        <v>7.541037114213366</v>
+        <v>7.538624378746964</v>
       </c>
       <c r="O267" s="2" t="n">
-        <v>0.3142534494371473</v>
+        <v>0.3141529048527072</v>
       </c>
     </row>
     <row r="268">
@@ -17603,28 +17603,28 @@
         <v>0</v>
       </c>
       <c r="H268" s="2" t="n">
-        <v>2.323717962098368</v>
+        <v>2.333883247194549</v>
       </c>
       <c r="I268" s="2" t="n">
         <v>4798.899130329469</v>
       </c>
       <c r="J268" s="2" t="n">
-        <v>11151.28810744482</v>
+        <v>11200.07028525244</v>
       </c>
       <c r="K268" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L268" s="2" t="n">
-        <v>3.163459071527198</v>
+        <v>3.17390745392926</v>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1.432100621672069</v>
+        <v>1.438365457311834</v>
       </c>
       <c r="N268" s="2" t="n">
-        <v>0.01064401152428501</v>
+        <v>0.01069057458119476</v>
       </c>
       <c r="O268" s="2" t="n">
-        <v>1.35205418401181</v>
+        <v>1.355739515515401</v>
       </c>
     </row>
     <row r="269">
@@ -17660,28 +17660,28 @@
         <v>0</v>
       </c>
       <c r="H269" s="2" t="n">
-        <v>17.48559188222232</v>
+        <v>17.43541401974733</v>
       </c>
       <c r="I269" s="2" t="n">
         <v>445.9483457946769</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>7797.670775117873</v>
+        <v>7775.294040351642</v>
       </c>
       <c r="K269" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L269" s="2" t="n">
-        <v>2.212086362817634</v>
+        <v>2.203384718367204</v>
       </c>
       <c r="M269" s="2" t="n">
-        <v>181.9879758792969</v>
+        <v>181.4657306108907</v>
       </c>
       <c r="N269" s="2" t="n">
-        <v>0.0006979301961252089</v>
+        <v>0.0006959273674171962</v>
       </c>
       <c r="O269" s="2" t="n">
-        <v>3.275508476152933</v>
+        <v>3.266108850737957</v>
       </c>
     </row>
     <row r="270">
@@ -17717,28 +17717,28 @@
         <v>0</v>
       </c>
       <c r="H270" s="2" t="n">
-        <v>119.5793417153552</v>
+        <v>119.5488095777085</v>
       </c>
       <c r="I270" s="2" t="n">
         <v>57.55493465680681</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>6882.381198731238</v>
+        <v>6880.623923544053</v>
       </c>
       <c r="K270" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L270" s="2" t="n">
-        <v>1.952431954681456</v>
+        <v>1.949850581507154</v>
       </c>
       <c r="M270" s="2" t="n">
-        <v>6.065187495534568</v>
+        <v>6.063638874035152</v>
       </c>
       <c r="N270" s="2" t="n">
-        <v>0.04057378159515082</v>
+        <v>0.04056342191038639</v>
       </c>
       <c r="O270" s="2" t="n">
-        <v>2.877505979783693</v>
+        <v>2.876771267521579</v>
       </c>
     </row>
     <row r="271">
@@ -17774,28 +17774,28 @@
         <v>0</v>
       </c>
       <c r="H271" s="2" t="n">
-        <v>139.4610812111397</v>
+        <v>137.9160849971049</v>
       </c>
       <c r="I271" s="2" t="n">
         <v>43.87420945614248</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>6118.74468803764</v>
+        <v>6050.959200534129</v>
       </c>
       <c r="K271" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L271" s="2" t="n">
-        <v>1.735799326788876</v>
+        <v>1.714737856179823</v>
       </c>
       <c r="M271" s="2" t="n">
-        <v>28.84787855797251</v>
+        <v>28.52829217037291</v>
       </c>
       <c r="N271" s="2" t="n">
-        <v>0.001748387031698327</v>
+        <v>0.001729017819003412</v>
       </c>
       <c r="O271" s="2" t="n">
-        <v>3.355931629791194</v>
+        <v>3.318753503696378</v>
       </c>
     </row>
   </sheetData>
@@ -19147,22 +19147,22 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1381.836663304188</v>
+        <v>1383.133752563955</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>72.37771418212461</v>
+        <v>72.51918056594202</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>282974.4314910982</v>
+        <v>283630.2800182434</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>73.99568751962109</v>
+        <v>74.02251137290011</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>204.7813891509161</v>
+        <v>205.0635229546454</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>130480.771620463</v>
+        <v>130486.0827273468</v>
       </c>
     </row>
     <row r="39">
@@ -19182,19 +19182,19 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>527.3651938131304</v>
+        <v>524.1323552022034</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>27.62228581787538</v>
+        <v>27.48081943405796</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>99445.73511126394</v>
+        <v>99537.31961831992</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>26.00431248037894</v>
+        <v>25.97748862709991</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>188.5709111597193</v>
+        <v>189.9087484876215</v>
       </c>
       <c r="I39" s="2" t="n">
         <v>0</v>
@@ -19217,22 +19217,22 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1398.586171388512</v>
+        <v>1398.956195226613</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>71.559978753007</v>
+        <v>71.59929730776166</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>125166.0302746638</v>
+        <v>125353.1212499976</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>61.91766292428422</v>
+        <v>61.9455101819997</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>89.49468601594951</v>
+        <v>89.60475079757018</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>60372.10014889469</v>
+        <v>60373.69348095982</v>
       </c>
     </row>
     <row r="41">
@@ -19252,19 +19252,19 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>555.8389077689386</v>
+        <v>554.9124149824435</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>28.44002124699299</v>
+        <v>28.40070269223835</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>76983.12129735632</v>
+        <v>77007.18037913172</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>38.08233707571578</v>
+        <v>38.05448981800031</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>138.4989791491136</v>
+        <v>138.7735763337861</v>
       </c>
       <c r="I41" s="2" t="n">
         <v>0</v>
@@ -19287,22 +19287,22 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1381.930314210203</v>
+        <v>1382.385988666276</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>65.34078725868214</v>
+        <v>65.38317777402951</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>257341.4658703298</v>
+        <v>257571.8751482602</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>75.69918294379477</v>
+        <v>75.70785894192952</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>186.2188441950526</v>
+        <v>186.3241361385363</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>178331.2335273423</v>
+        <v>178333.0924147516</v>
       </c>
     </row>
     <row r="43">
@@ -19322,19 +19322,19 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>733.0278492707229</v>
+        <v>731.8978924933913</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>34.65921274131784</v>
+        <v>34.6168222259705</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>82611.29961909569</v>
+        <v>82646.27227792254</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>24.30081705620524</v>
+        <v>24.2921410580705</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>112.6987190204087</v>
+        <v>112.9204949564311</v>
       </c>
       <c r="I43" s="2" t="n">
         <v>0</v>
@@ -19357,22 +19357,22 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1403.365265473746</v>
+        <v>1403.565424091987</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>73.18408068575002</v>
+        <v>73.20586404467116</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>144213.466990081</v>
+        <v>144314.675025019</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>69.04803309476527</v>
+        <v>69.05810796778231</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>102.7626025369793</v>
+        <v>102.8200556581685</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>92228.50207456989</v>
+        <v>92229.38725905052</v>
       </c>
     </row>
     <row r="45">
@@ -19392,19 +19392,19 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>514.2174278168201</v>
+        <v>513.7200863085366</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>26.81591931425</v>
+        <v>26.79413595532883</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>64646.16380078402</v>
+        <v>64661.04016883792</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>30.95196690523475</v>
+        <v>30.94189203221768</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>125.7175667406842</v>
+        <v>125.8682342625065</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>0</v>
@@ -19427,22 +19427,22 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1399.981978432327</v>
+        <v>1400.151277335299</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>71.18760682003143</v>
+        <v>71.20526816005234</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>86738.10448239293</v>
+        <v>86823.71006856073</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>53.69737955742512</v>
+        <v>53.71750653067743</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>61.95658645514894</v>
+        <v>62.01023523243821</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>40826.46614562507</v>
+        <v>40827.26281165763</v>
       </c>
     </row>
     <row r="47">
@@ -19462,19 +19462,19 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>566.6271561767422</v>
+        <v>566.2078327632615</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>28.81239317996856</v>
+        <v>28.79473183994766</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>74793.24992873499</v>
+        <v>74806.48402649975</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46.30262044257488</v>
+        <v>46.28249346932256</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>131.9972915406926</v>
+        <v>132.1184195941303</v>
       </c>
       <c r="I47" s="2" t="n">
         <v>0</v>
@@ -19497,22 +19497,22 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1406.888618608744</v>
+        <v>1407.460208297674</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>72.06455309709736</v>
+        <v>72.1254409100633</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>210554.046905864</v>
+        <v>210843.0576271448</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>72.88573654308946</v>
+        <v>72.90297511127595</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>149.6593576214146</v>
+        <v>149.8039208384867</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>122117.5116210804</v>
+        <v>122119.9016191781</v>
       </c>
     </row>
     <row r="49">
@@ -19532,19 +19532,19 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>545.3730109238079</v>
+        <v>543.9458289322461</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>27.93544690290263</v>
+        <v>27.87455908993668</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>78328.32829162902</v>
+        <v>78367.44071715878</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>27.11426345691053</v>
+        <v>27.09702488872405</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>143.6234040238782</v>
+        <v>144.0721420200838</v>
       </c>
       <c r="I49" s="2" t="n">
         <v>0</v>
@@ -19567,22 +19567,22 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1399.451525393135</v>
+        <v>1400.08779552882</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>72.04514502239024</v>
+        <v>72.11323942309684</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>200128.0099419135</v>
+        <v>200449.7253461142</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>71.18222826852245</v>
+        <v>71.20408863469163</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>143.0046030966977</v>
+        <v>143.1693969379994</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>107532.294217767</v>
+        <v>107534.9497712089</v>
       </c>
     </row>
     <row r="51">
@@ -19602,19 +19602,19 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>543.0131958010727</v>
+        <v>541.4250344722572</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>27.95485497760977</v>
+        <v>27.88676057690316</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>81020.83129267913</v>
+        <v>81064.62191912456</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>28.81777173147754</v>
+        <v>28.79591136530838</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>149.2060081029049</v>
+        <v>149.7245542000854</v>
       </c>
       <c r="I51" s="2" t="n">
         <v>0</v>
@@ -19637,22 +19637,22 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1400.50743876489</v>
+        <v>1400.941647904692</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>66.52743534233355</v>
+        <v>66.56841863932067</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>287678.7192170005</v>
+        <v>287898.273329167</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>78.52254210216036</v>
+        <v>78.52839780357866</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>205.4103471743819</v>
+        <v>205.5034010586807</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>206819.2000511457</v>
+        <v>206820.970420107</v>
       </c>
     </row>
     <row r="53">
@@ -19672,19 +19672,19 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>704.650277834629</v>
+        <v>703.5722890948318</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>33.47256465766647</v>
+        <v>33.43158136067934</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>78685.78136516512</v>
+        <v>78718.49382974101</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>21.47745789783966</v>
+        <v>21.47160219642134</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>111.6664306256493</v>
+        <v>111.8840168236513</v>
       </c>
       <c r="I53" s="2" t="n">
         <v>0</v>
@@ -19707,22 +19707,22 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1383.766174787601</v>
+        <v>1384.416032832909</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>66.97906088043744</v>
+        <v>67.04184969210613</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>266356.2165165095</v>
+        <v>266684.8094360136</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>75.56140432191626</v>
+        <v>75.57389221326569</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>192.4864340302244</v>
+        <v>192.6334303499076</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>170014.9224014508</v>
+        <v>170017.5779548927</v>
       </c>
     </row>
     <row r="55">
@@ -19742,19 +19742,19 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>682.2021391870086</v>
+        <v>680.5867067855913</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>33.02093911956254</v>
+        <v>32.95815030789385</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>86146.78274187523</v>
+        <v>86194.73881253046</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>24.43859567808376</v>
+        <v>24.4261077867343</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>126.2775030939331</v>
+        <v>126.6476966904451</v>
       </c>
       <c r="I55" s="2" t="n">
         <v>0</v>
@@ -20318,19 +20318,19 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>382420.1666023621</v>
+        <v>383167.5996365633</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>130480.771620463</v>
+        <v>130486.0827273468</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>251939.394981899</v>
+        <v>252681.5169092165</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>34.11974132528844</v>
+        <v>34.0545711200826</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>65.88025867471156</v>
+        <v>65.9454288799174</v>
       </c>
     </row>
     <row r="21">
@@ -20345,19 +20345,19 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>202149.1515720201</v>
+        <v>202360.3016291293</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>60372.1001488947</v>
+        <v>60373.69348095982</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>141777.0514231254</v>
+        <v>141986.6081481695</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>29.86512665495201</v>
+        <v>29.83475167555748</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>70.13487334504799</v>
+        <v>70.16524832444252</v>
       </c>
     </row>
     <row r="22">
@@ -20372,19 +20372,19 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>339952.7654894255</v>
+        <v>340218.1474261827</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>178331.2335273424</v>
+        <v>178333.0924147516</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>161621.5319620831</v>
+        <v>161885.0550114311</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>52.45765048288437</v>
+        <v>52.41727807992507</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>47.54234951711563</v>
+        <v>47.58272192007493</v>
       </c>
     </row>
     <row r="23">
@@ -20399,19 +20399,19 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>208859.630790865</v>
+        <v>208975.7151938569</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>92228.50207456989</v>
+        <v>92229.38725905052</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>116631.1287162951</v>
+        <v>116746.3279348064</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>44.1581275066602</v>
+        <v>44.13402158882129</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>55.8418724933398</v>
+        <v>55.86597841117871</v>
       </c>
     </row>
     <row r="24">
@@ -20426,19 +20426,19 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>161531.3544111279</v>
+        <v>161630.1940950605</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>40826.46614562507</v>
+        <v>40827.26281165763</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>120704.8882655028</v>
+        <v>120802.9312834029</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>25.27463865728134</v>
+        <v>25.2596756690434</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>74.72536134271866</v>
+        <v>74.7403243309566</v>
       </c>
     </row>
     <row r="25">
@@ -20453,19 +20453,19 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>288882.375197493</v>
+        <v>289210.4983443036</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>122117.5116210804</v>
+        <v>122119.9016191781</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>166764.8635764127</v>
+        <v>167090.5967251255</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>42.2723994627901</v>
+        <v>42.2252657902463</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>57.7276005372099</v>
+        <v>57.7747342097537</v>
       </c>
     </row>
     <row r="26">
@@ -20480,19 +20480,19 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>281148.8412345927</v>
+        <v>281514.3472652387</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>107532.294217767</v>
+        <v>107534.9497712089</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>173616.5470168256</v>
+        <v>173979.3974940298</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>38.24746128974485</v>
+        <v>38.19874575340598</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>61.75253871025515</v>
+        <v>61.80125424659402</v>
       </c>
     </row>
     <row r="27">
@@ -20507,19 +20507,19 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>366364.5005821656</v>
+        <v>366616.7671589081</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>206819.2000511457</v>
+        <v>206820.9704201069</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>159545.3005310199</v>
+        <v>159795.7967388011</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>56.45175766825196</v>
+        <v>56.41339648016194</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>43.54824233174804</v>
+        <v>43.58660351983806</v>
       </c>
     </row>
     <row r="28">
@@ -20534,19 +20534,19 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>352502.9992583847</v>
+        <v>352879.548248544</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>170014.9224014508</v>
+        <v>170017.5779548927</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>182488.0768569339</v>
+        <v>182861.9702936514</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>48.23077328679121</v>
+        <v>48.18005996628175</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>51.76922671320879</v>
+        <v>51.81994003371825</v>
       </c>
     </row>
   </sheetData>
@@ -21321,10 +21321,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F20" t="n">
-        <v>970.2255008807361</v>
+        <v>974.5334493114932</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -21359,10 +21359,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.02977449911926392</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F21" t="n">
-        <v>29.77449911926392</v>
+        <v>25.46655068850678</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -21397,10 +21397,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F22" t="n">
-        <v>291.0676502642208</v>
+        <v>292.3600347934479</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -21435,10 +21435,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.02977449911926392</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F23" t="n">
-        <v>8.932349735779175</v>
+        <v>7.639965206552034</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -21473,10 +21473,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F24" t="n">
-        <v>339.5789253082576</v>
+        <v>341.0867072590226</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -21511,10 +21511,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.02977449911926392</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F25" t="n">
-        <v>10.42107469174237</v>
+        <v>8.913292740977374</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -21549,10 +21549,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F26" t="n">
-        <v>161.7042501467893</v>
+        <v>162.4222415519155</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -21587,10 +21587,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.02977449911926392</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F27" t="n">
-        <v>4.962416519877319</v>
+        <v>4.24442511475113</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -21625,10 +21625,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F28" t="n">
-        <v>145.5338251321104</v>
+        <v>146.180017396724</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -21663,10 +21663,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.02977449911926392</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F29" t="n">
-        <v>4.466174867889587</v>
+        <v>3.819982603276017</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -21701,10 +21701,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F30" t="n">
-        <v>436.6014753963312</v>
+        <v>438.5400521901719</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -21739,10 +21739,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.02977449911926392</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F31" t="n">
-        <v>13.39852460366876</v>
+        <v>11.45994780982805</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -21777,10 +21777,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F32" t="n">
-        <v>485.1127504403681</v>
+        <v>487.2667246557466</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -21815,10 +21815,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.02977449911926392</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F33" t="n">
-        <v>14.88724955963196</v>
+        <v>12.73327534425339</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -21853,10 +21853,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F34" t="n">
-        <v>323.4085002935786</v>
+        <v>324.844483103831</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -21891,10 +21891,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.02977449911926392</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F35" t="n">
-        <v>9.924833039754636</v>
+        <v>8.488850229502258</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -21929,10 +21929,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9702255008807361</v>
+        <v>0.9745334493114932</v>
       </c>
       <c r="F36" t="n">
-        <v>485.1127504403681</v>
+        <v>487.2667246557466</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -21967,10 +21967,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.02977449911926392</v>
+        <v>0.02546655068850678</v>
       </c>
       <c r="F37" t="n">
-        <v>14.88724955963196</v>
+        <v>12.73327534425339</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -22689,10 +22689,10 @@
         <v>1000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1.13686837721616e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -22723,10 +22723,10 @@
         <v>1000</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1.13686837721616e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -23601,16 +23601,16 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1909.201857117318</v>
+        <v>1907.266107766158</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>1925.037208036543</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>-15.83535091922545</v>
+        <v>-17.77110027038498</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>-0.8225997322605955</v>
+        <v>-0.9231561964722099</v>
       </c>
     </row>
     <row r="48">
@@ -23635,16 +23635,16 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>1954.42507915745</v>
+        <v>1953.868610209056</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>1959.352995174775</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>-4.927916017324151</v>
+        <v>-5.484384965718164</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>-0.2515073102937523</v>
+        <v>-0.2799079583528008</v>
       </c>
     </row>
     <row r="49">
@@ -23669,16 +23669,16 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2114.958163480926</v>
+        <v>2114.283881159667</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>2120.558269623172</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>-5.600106142246204</v>
+        <v>-6.274388463505147</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>-0.2640864069838249</v>
+        <v>-0.295883803495771</v>
       </c>
     </row>
     <row r="50">
@@ -23703,16 +23703,16 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1917.582693290566</v>
+        <v>1917.285510400524</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>1920.371028203399</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>-2.788334912833534</v>
+        <v>-3.085517802875302</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>-0.1451977181431527</v>
+        <v>-0.1606730031624125</v>
       </c>
     </row>
     <row r="51">
@@ -23737,16 +23737,16 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1966.609134609069</v>
+        <v>1966.35911009856</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>1969.206216134805</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>-2.597081525735575</v>
+        <v>-2.84710603624444</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>-0.1318846906157536</v>
+        <v>-0.1445814060973662</v>
       </c>
     </row>
     <row r="52">
@@ -23771,16 +23771,16 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1952.261629532552</v>
+        <v>1951.406037229921</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>1959.488267660658</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>-7.226638128105606</v>
+        <v>-8.082230430737127</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>-0.3688023167769794</v>
+        <v>-0.4124663854398131</v>
       </c>
     </row>
     <row r="53">
@@ -23805,16 +23805,16 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1942.464721194208</v>
+        <v>1941.512830001077</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>1950.482397570457</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>-8.017676376249256</v>
+        <v>-8.969567569380388</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>-0.4110612013846505</v>
+        <v>-0.4598640613497965</v>
       </c>
     </row>
     <row r="54">
@@ -23839,16 +23839,16 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2105.157716599519</v>
+        <v>2104.513936999524</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>2110.486101250903</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>-5.328384651383658</v>
+        <v>-5.972164251378672</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>-0.2524719138508176</v>
+        <v>-0.282975767897212</v>
       </c>
     </row>
     <row r="55">
@@ -23873,16 +23873,16 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2065.96831397461</v>
+        <v>2065.002739618501</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>2073.929471749065</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>-7.961157774454932</v>
+        <v>-8.926732130564233</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>-0.383868298459582</v>
+        <v>-0.4304260223003535</v>
       </c>
     </row>
     <row r="56">
@@ -24519,16 +24519,16 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1381.836663304188</v>
+        <v>1383.133752563955</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>1357.011889879685</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>24.82477342450284</v>
+        <v>26.12186268427013</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>1.829370369533302</v>
+        <v>1.924954591708562</v>
       </c>
     </row>
     <row r="75">
@@ -24553,16 +24553,16 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1398.586171388512</v>
+        <v>1398.956195226613</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>1391.315291678854</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>7.270879709657493</v>
+        <v>7.640903547759081</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>0.5225903684910961</v>
+        <v>0.5491856226591928</v>
       </c>
     </row>
     <row r="76">
@@ -24587,16 +24587,16 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>1381.930314210203</v>
+        <v>1382.385988666276</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>1373.233833189604</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>8.696481020598412</v>
+        <v>9.152155476671396</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0.6332847917385733</v>
+        <v>0.6664673747087723</v>
       </c>
     </row>
     <row r="77">
@@ -24621,16 +24621,16 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1403.365265473746</v>
+        <v>1403.565424091987</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>1399.362770181232</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>4.002495292513686</v>
+        <v>4.202653910755089</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.2860227081784747</v>
+        <v>0.3003262628039476</v>
       </c>
     </row>
     <row r="78">
@@ -24655,16 +24655,16 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>1399.981978432327</v>
+        <v>1400.151277335299</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>1396.490202628138</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>3.491775804188819</v>
+        <v>3.661074707160878</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0.2500394057629218</v>
+        <v>0.2621625773149632</v>
       </c>
     </row>
     <row r="79">
@@ -24689,16 +24689,16 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>1406.888618608744</v>
+        <v>1407.460208297674</v>
       </c>
       <c r="F79" s="2" t="n">
         <v>1395.813705000742</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>11.07491360800259</v>
+        <v>11.64650329693268</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>0.7934378039365005</v>
+        <v>0.8343880888407303</v>
       </c>
     </row>
     <row r="80">
@@ -24723,16 +24723,16 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1399.451525393135</v>
+        <v>1400.08779552882</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>1387.137915327889</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>12.31361006524685</v>
+        <v>12.94988020093115</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>0.8876990477429337</v>
+        <v>0.9335683249541978</v>
       </c>
     </row>
     <row r="81">
@@ -24757,16 +24757,16 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1400.50743876489</v>
+        <v>1400.941647904692</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>1392.219650153417</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>8.287788611472934</v>
+        <v>8.721997751275239</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>0.5952931788141083</v>
+        <v>0.6264814428035195</v>
       </c>
     </row>
     <row r="82">
@@ -24791,16 +24791,16 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1383.766174787601</v>
+        <v>1384.416032832909</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>1371.347294780337</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>12.41888000726385</v>
+        <v>13.06873805257146</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>0.9055970033654466</v>
+        <v>0.9529852942660171</v>
       </c>
     </row>
     <row r="83">
@@ -25437,16 +25437,16 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>527.3651938131304</v>
+        <v>524.1323552022034</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>568.0253181568588</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>-40.6601243437284</v>
+        <v>-43.89296295465545</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>-7.158153526618016</v>
+        <v>-7.727289885084755</v>
       </c>
     </row>
     <row r="102">
@@ -25471,16 +25471,16 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>555.8389077689386</v>
+        <v>554.9124149824435</v>
       </c>
       <c r="F102" s="2" t="n">
         <v>568.0377034959201</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>-12.19879572698153</v>
+        <v>-13.12528851347668</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>-2.147532752122878</v>
+        <v>-2.310636852571345</v>
       </c>
     </row>
     <row r="103">
@@ -25505,16 +25505,16 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>733.0278492707229</v>
+        <v>731.8978924933913</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>747.3244364335677</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>-14.29658716284484</v>
+        <v>-15.42654394017643</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>-1.913036221734162</v>
+        <v>-2.064236520057611</v>
       </c>
     </row>
     <row r="104">
@@ -25539,16 +25539,16 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>514.2174278168201</v>
+        <v>513.7200863085366</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>521.0082580221671</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>-6.790830205346992</v>
+        <v>-7.288171713630504</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>-1.303401644942462</v>
+        <v>-1.398859154612559</v>
       </c>
     </row>
     <row r="105">
@@ -25573,16 +25573,16 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>566.6271561767422</v>
+        <v>566.2078327632615</v>
       </c>
       <c r="F105" s="2" t="n">
         <v>572.7160135066665</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>-6.088857329924281</v>
+        <v>-6.508180743404978</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>-1.063154720023104</v>
+        <v>-1.136371358564993</v>
       </c>
     </row>
     <row r="106">
@@ -25607,16 +25607,16 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>545.3730109238079</v>
+        <v>543.9458289322461</v>
       </c>
       <c r="F106" s="2" t="n">
         <v>563.6745626599162</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>-18.30155173610831</v>
+        <v>-19.72873372767015</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>-3.246829455944467</v>
+        <v>-3.500022004642624</v>
       </c>
     </row>
     <row r="107">
@@ -25641,16 +25641,16 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>543.0131958010727</v>
+        <v>541.4250344722572</v>
       </c>
       <c r="F107" s="2" t="n">
         <v>563.3444822425687</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>-20.33128644149599</v>
+        <v>-21.91944777031154</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>-3.609032675808051</v>
+        <v>-3.890949225783543</v>
       </c>
     </row>
     <row r="108">
@@ -25675,16 +25675,16 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>704.650277834629</v>
+        <v>703.5722890948318</v>
       </c>
       <c r="F108" s="2" t="n">
         <v>718.2664510974853</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>-13.61617326285625</v>
+        <v>-14.69416200265346</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>-1.895699463903852</v>
+        <v>-2.045781475690714</v>
       </c>
     </row>
     <row r="109">
@@ -25709,16 +25709,16 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>682.2021391870086</v>
+        <v>680.5867067855913</v>
       </c>
       <c r="F109" s="2" t="n">
         <v>702.5821769687275</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>-20.3800377817189</v>
+        <v>-21.99547018313615</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>-2.900733672130432</v>
+        <v>-3.130661565887571</v>
       </c>
     </row>
     <row r="110">
@@ -26355,16 +26355,16 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>382420.1666023621</v>
+        <v>383167.5996365633</v>
       </c>
       <c r="F128" s="2" t="n">
         <v>428113.5341067808</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>-45693.36750441877</v>
+        <v>-44945.93447021756</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>-10.67318920429688</v>
+        <v>-10.4986016300543</v>
       </c>
     </row>
     <row r="129">
@@ -26389,16 +26389,16 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>202149.1515720201</v>
+        <v>202360.3016291293</v>
       </c>
       <c r="F129" s="2" t="n">
         <v>216406.9710876753</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>-14257.81951565514</v>
+        <v>-14046.66945854592</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>-6.588428942004238</v>
+        <v>-6.490858121596759</v>
       </c>
     </row>
     <row r="130">
@@ -26423,16 +26423,16 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>339952.7654894255</v>
+        <v>340218.1474261827</v>
       </c>
       <c r="F130" s="2" t="n">
         <v>356045.7240370425</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>-16092.95854761708</v>
+        <v>-15827.57661085983</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>-4.519913444022371</v>
+        <v>-4.445377529435841</v>
       </c>
     </row>
     <row r="131">
@@ -26457,16 +26457,16 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>208859.630790865</v>
+        <v>208975.7151938569</v>
       </c>
       <c r="F131" s="2" t="n">
         <v>216987.1565901284</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>-8127.525799263443</v>
+        <v>-8011.441396271519</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>-3.745625283534959</v>
+        <v>-3.692127000587642</v>
       </c>
     </row>
     <row r="132">
@@ -26491,16 +26491,16 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>161531.3544111279</v>
+        <v>161630.1940950605</v>
       </c>
       <c r="F132" s="2" t="n">
         <v>169090.0151412379</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>-7558.660730110016</v>
+        <v>-7459.821046177443</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>-4.470199333648647</v>
+        <v>-4.411745448095433</v>
       </c>
     </row>
     <row r="133">
@@ -26525,16 +26525,16 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>288882.375197493</v>
+        <v>289210.4983443036</v>
       </c>
       <c r="F133" s="2" t="n">
         <v>309794.8842831829</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>-20912.5090856899</v>
+        <v>-20584.38593887934</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>-6.75043719139462</v>
+        <v>-6.644520934071716</v>
       </c>
     </row>
     <row r="134">
@@ -26559,16 +26559,16 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>281148.8412345927</v>
+        <v>281514.3472652387</v>
       </c>
       <c r="F134" s="2" t="n">
         <v>304336.5491684119</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>-23187.70793381921</v>
+        <v>-22822.20190317318</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>-7.619100629608487</v>
+        <v>-7.499001340960849</v>
       </c>
     </row>
     <row r="135">
@@ -26593,16 +26593,16 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>366364.5005821656</v>
+        <v>366616.7671589081</v>
       </c>
       <c r="F135" s="2" t="n">
         <v>381702.8635022599</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>-15338.3629200944</v>
+        <v>-15086.09634335188</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>-4.018403943674786</v>
+        <v>-3.952314165246643</v>
       </c>
     </row>
     <row r="136">
@@ -26627,16 +26627,16 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>352502.9992583847</v>
+        <v>352879.548248544</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>375427.2603331699</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>-22924.2610747852</v>
+        <v>-22547.71208462585</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>-6.106179144913784</v>
+        <v>-6.005880357386958</v>
       </c>
     </row>
     <row r="137">
@@ -27273,16 +27273,16 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>282974.4314910982</v>
+        <v>283630.2800182434</v>
       </c>
       <c r="F155" s="2" t="n">
         <v>339326.4139217038</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>-56351.98243060557</v>
+        <v>-55696.13390346034</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>-16.60701322344103</v>
+        <v>-16.41373368485003</v>
       </c>
     </row>
     <row r="156">
@@ -27307,16 +27307,16 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>125166.0302746638</v>
+        <v>125353.1212499976</v>
       </c>
       <c r="F156" s="2" t="n">
         <v>142390.025306692</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>-17223.99503202819</v>
+        <v>-17036.90405669439</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>-12.09634944226582</v>
+        <v>-11.96495612666605</v>
       </c>
     </row>
     <row r="157">
@@ -27341,16 +27341,16 @@
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>257341.4658703298</v>
+        <v>257571.8751482602</v>
       </c>
       <c r="F157" s="2" t="n">
         <v>277141.446043731</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>-19799.98017340124</v>
+        <v>-19569.57089547082</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>-7.144359119161463</v>
+        <v>-7.061221327532108</v>
       </c>
     </row>
     <row r="158">
@@ -27375,16 +27375,16 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>144213.466990081</v>
+        <v>144314.675025019</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>153932.2324693588</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>-9718.765479277819</v>
+        <v>-9617.557444339851</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>-6.313664996193959</v>
+        <v>-6.247916560460647</v>
       </c>
     </row>
     <row r="159">
@@ -27409,16 +27409,16 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>86738.10448239293</v>
+        <v>86823.71006856073</v>
       </c>
       <c r="F159" s="2" t="n">
         <v>95597.21893998417</v>
       </c>
       <c r="G159" s="2" t="n">
-        <v>-8859.114457591248</v>
+        <v>-8773.508871423444</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>-9.267125713304473</v>
+        <v>-9.17757751606921</v>
       </c>
     </row>
     <row r="160">
@@ -27443,16 +27443,16 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>210554.046905864</v>
+        <v>210843.0576271448</v>
       </c>
       <c r="F160" s="2" t="n">
         <v>236133.8367712313</v>
       </c>
       <c r="G160" s="2" t="n">
-        <v>-25579.78986536732</v>
+        <v>-25290.7791440865</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>-10.83275070406333</v>
+        <v>-10.71035794357098</v>
       </c>
     </row>
     <row r="161">
@@ -27477,16 +27477,16 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>200128.0099419135</v>
+        <v>200449.7253461142</v>
       </c>
       <c r="F161" s="2" t="n">
         <v>228514.5085635225</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>-28386.498621609</v>
+        <v>-28064.78321740835</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>-12.42218658239729</v>
+        <v>-12.28140103393343</v>
       </c>
     </row>
     <row r="162">
@@ -27511,16 +27511,16 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>287678.7192170005</v>
+        <v>287898.273329167</v>
       </c>
       <c r="F162" s="2" t="n">
         <v>306553.9278759986</v>
       </c>
       <c r="G162" s="2" t="n">
-        <v>-18875.20865899813</v>
+        <v>-18655.65454683156</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>-6.157222903577727</v>
+        <v>-6.085602841917521</v>
       </c>
     </row>
     <row r="163">
@@ -27545,16 +27545,16 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>266356.2165165095</v>
+        <v>266684.8094360136</v>
       </c>
       <c r="F163" s="2" t="n">
         <v>294592.5200651514</v>
       </c>
       <c r="G163" s="2" t="n">
-        <v>-28236.30354864191</v>
+        <v>-27907.71062913787</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>-9.584867783607416</v>
+        <v>-9.47332628233937</v>
       </c>
     </row>
     <row r="164">
@@ -28191,16 +28191,16 @@
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>99445.73511126394</v>
+        <v>99537.31961831992</v>
       </c>
       <c r="F182" s="2" t="n">
         <v>88787.12018507704</v>
       </c>
       <c r="G182" s="2" t="n">
-        <v>10658.6149261869</v>
+        <v>10750.19943324287</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>12.00468593188852</v>
+        <v>12.10783659931086</v>
       </c>
     </row>
     <row r="183">
@@ -28225,16 +28225,16 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>76983.12129735632</v>
+        <v>77007.18037913172</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>74016.94578098327</v>
       </c>
       <c r="G183" s="2" t="n">
-        <v>2966.175516373056</v>
+        <v>2990.234598148454</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>4.007427603335583</v>
+        <v>4.039932432495367</v>
       </c>
     </row>
     <row r="184">
@@ -28259,16 +28259,16 @@
         </is>
       </c>
       <c r="E184" s="2" t="n">
-        <v>82611.29961909569</v>
+        <v>82646.27227792254</v>
       </c>
       <c r="F184" s="2" t="n">
         <v>78904.27799331152</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>3707.021625784168</v>
+        <v>3741.994284611021</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>4.698125019404398</v>
+        <v>4.742447912555791</v>
       </c>
     </row>
     <row r="185">
@@ -28293,16 +28293,16 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>64646.16380078402</v>
+        <v>64661.04016883792</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>63054.9241207696</v>
       </c>
       <c r="G185" s="2" t="n">
-        <v>1591.239680014427</v>
+        <v>1606.116048068325</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>2.523577186401356</v>
+        <v>2.547169900628408</v>
       </c>
     </row>
     <row r="186">
@@ -28327,16 +28327,16 @@
         </is>
       </c>
       <c r="E186" s="2" t="n">
-        <v>74793.24992873499</v>
+        <v>74806.48402649975</v>
       </c>
       <c r="F186" s="2" t="n">
         <v>73492.79620125376</v>
       </c>
       <c r="G186" s="2" t="n">
-        <v>1300.453727481232</v>
+        <v>1313.687825245986</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>1.76949822935033</v>
+        <v>1.787505569455494</v>
       </c>
     </row>
     <row r="187">
@@ -28361,16 +28361,16 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>78328.32829162902</v>
+        <v>78367.44071715878</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>73661.0475119516</v>
       </c>
       <c r="G187" s="2" t="n">
-        <v>4667.280779677414</v>
+        <v>4706.393205207176</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>6.336158576783939</v>
+        <v>6.389256417299194</v>
       </c>
     </row>
     <row r="188">
@@ -28395,16 +28395,16 @@
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>81020.83129267913</v>
+        <v>81064.62191912456</v>
       </c>
       <c r="F188" s="2" t="n">
         <v>75822.04060488936</v>
       </c>
       <c r="G188" s="2" t="n">
-        <v>5198.790687789762</v>
+        <v>5242.581314235198</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>6.856569206414262</v>
+        <v>6.914323687955625</v>
       </c>
     </row>
     <row r="189">
@@ -28429,16 +28429,16 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>78685.78136516512</v>
+        <v>78718.49382974101</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>75148.93562626136</v>
       </c>
       <c r="G189" s="2" t="n">
-        <v>3536.845738903765</v>
+        <v>3569.558203479653</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>4.706448214374692</v>
+        <v>4.749978391220546</v>
       </c>
     </row>
     <row r="190">
@@ -28463,16 +28463,16 @@
         </is>
       </c>
       <c r="E190" s="2" t="n">
-        <v>86146.78274187523</v>
+        <v>86194.73881253046</v>
       </c>
       <c r="F190" s="2" t="n">
         <v>80834.74026801846</v>
       </c>
       <c r="G190" s="2" t="n">
-        <v>5312.042473856767</v>
+        <v>5359.998544511996</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>6.571484557560246</v>
+        <v>6.630810622685494</v>
       </c>
     </row>
     <row r="191">
@@ -29109,16 +29109,16 @@
         </is>
       </c>
       <c r="E209" s="2" t="n">
-        <v>200.3036845877438</v>
+        <v>200.8988667477238</v>
       </c>
       <c r="F209" s="2" t="n">
         <v>222.3923425061683</v>
       </c>
       <c r="G209" s="2" t="n">
-        <v>-22.08865791842442</v>
+        <v>-21.49347575844448</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>-9.932292483412176</v>
+        <v>-9.664665391007485</v>
       </c>
     </row>
     <row r="210">
@@ -29143,16 +29143,16 @@
         </is>
       </c>
       <c r="E210" s="2" t="n">
-        <v>103.4315173949601</v>
+        <v>103.5690427553762</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>110.4481793840174</v>
       </c>
       <c r="G210" s="2" t="n">
-        <v>-7.016661989057283</v>
+        <v>-6.879136628641135</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>-6.352899638717489</v>
+        <v>-6.228383905472138</v>
       </c>
     </row>
     <row r="211">
@@ -29177,16 +29177,16 @@
         </is>
       </c>
       <c r="E211" s="2" t="n">
-        <v>160.7373476030896</v>
+        <v>160.9141281631377</v>
       </c>
       <c r="F211" s="2" t="n">
         <v>167.9018818475159</v>
       </c>
       <c r="G211" s="2" t="n">
-        <v>-7.164534244426306</v>
+        <v>-6.98775368437822</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>-4.267095857170291</v>
+        <v>-4.16180784127501</v>
       </c>
     </row>
     <row r="212">
@@ -29211,16 +29211,16 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>108.9181872164598</v>
+        <v>108.9956159686418</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>112.9923089878785</v>
       </c>
       <c r="G212" s="2" t="n">
-        <v>-4.074121771418731</v>
+        <v>-3.996693019236687</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>-3.605662905654748</v>
+        <v>-3.53713722202583</v>
       </c>
     </row>
     <row r="213">
@@ -29245,16 +29245,16 @@
         </is>
       </c>
       <c r="E213" s="2" t="n">
-        <v>82.13698979041801</v>
+        <v>82.19769891724359</v>
       </c>
       <c r="F213" s="2" t="n">
         <v>85.86709393652586</v>
       </c>
       <c r="G213" s="2" t="n">
-        <v>-3.730104146107848</v>
+        <v>-3.669395019282277</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>-4.344043771721438</v>
+        <v>-4.273342500672894</v>
       </c>
     </row>
     <row r="214">
@@ -29279,16 +29279,16 @@
         </is>
       </c>
       <c r="E214" s="2" t="n">
-        <v>147.9731870090909</v>
+        <v>148.2062127648465</v>
       </c>
       <c r="F214" s="2" t="n">
         <v>158.0998924035573</v>
       </c>
       <c r="G214" s="2" t="n">
-        <v>-10.12670539446637</v>
+        <v>-9.893679638710836</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>-6.405257613090264</v>
+        <v>-6.257866142917264</v>
       </c>
     </row>
     <row r="215">
@@ -29313,16 +29313,16 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>144.7381968727572</v>
+        <v>144.9974179491168</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>156.0314256347542</v>
       </c>
       <c r="G215" s="2" t="n">
-        <v>-11.29322876199703</v>
+        <v>-11.03400768563739</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>-7.23779117960042</v>
+        <v>-7.071657290029716</v>
       </c>
     </row>
     <row r="216">
@@ -29347,16 +29347,16 @@
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>174.0318540949785</v>
+        <v>174.2049604487798</v>
       </c>
       <c r="F216" s="2" t="n">
         <v>180.8601645260878</v>
       </c>
       <c r="G216" s="2" t="n">
-        <v>-6.828310431109344</v>
+        <v>-6.655204077307985</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>-3.775464016082108</v>
+        <v>-3.679751201568778</v>
       </c>
     </row>
     <row r="217">
@@ -29381,16 +29381,16 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>170.6236232540384</v>
+        <v>170.8857530686554</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>181.0221926286386</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>-10.39856937460024</v>
+        <v>-10.13643955998319</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>-5.744361629699505</v>
+        <v>-5.599556282459675</v>
       </c>
     </row>
     <row r="218">
@@ -30027,16 +30027,16 @@
         </is>
       </c>
       <c r="E236" s="2" t="n">
-        <v>4.992419395869605</v>
+        <v>4.977628874610514</v>
       </c>
       <c r="F236" s="2" t="n">
         <v>4.496557699473237</v>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.4958616963963678</v>
+        <v>0.4810711751372772</v>
       </c>
       <c r="H236" s="2" t="n">
-        <v>11.02758442206706</v>
+        <v>10.69865455509742</v>
       </c>
     </row>
     <row r="237">
@@ -30061,16 +30061,16 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>9.668232906043848</v>
+        <v>9.65539483030599</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>9.054019772685423</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.6142131333584242</v>
+        <v>0.601375057620567</v>
       </c>
       <c r="H237" s="2" t="n">
-        <v>6.783872233319063</v>
+        <v>6.642078024115017</v>
       </c>
     </row>
     <row r="238">
@@ -30095,16 +30095,16 @@
         </is>
       </c>
       <c r="E238" s="2" t="n">
-        <v>6.221329485100815</v>
+        <v>6.214494720974295</v>
       </c>
       <c r="F238" s="2" t="n">
         <v>5.955859392381164</v>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.2654700927196512</v>
+        <v>0.2586353285931304</v>
       </c>
       <c r="H238" s="2" t="n">
-        <v>4.457292814186395</v>
+        <v>4.342535838303723</v>
       </c>
     </row>
     <row r="239">
@@ -30129,16 +30129,16 @@
         </is>
       </c>
       <c r="E239" s="2" t="n">
-        <v>9.181203117277731</v>
+        <v>9.174680936595664</v>
       </c>
       <c r="F239" s="2" t="n">
         <v>8.850159882185231</v>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.3310432350924994</v>
+        <v>0.3245210544104324</v>
       </c>
       <c r="H239" s="2" t="n">
-        <v>3.74053395079186</v>
+        <v>3.666838325301571</v>
       </c>
     </row>
     <row r="240">
@@ -30163,16 +30163,16 @@
         </is>
       </c>
       <c r="E240" s="2" t="n">
-        <v>12.17478267162718</v>
+        <v>12.1657906872405</v>
       </c>
       <c r="F240" s="2" t="n">
         <v>11.64590478325974</v>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.5288778883674414</v>
+        <v>0.5198859039807537</v>
       </c>
       <c r="H240" s="2" t="n">
-        <v>4.541320732139853</v>
+        <v>4.464109175339105</v>
       </c>
     </row>
     <row r="241">
@@ -30197,16 +30197,16 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>6.757981092470243</v>
+        <v>6.747355467389646</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>6.325114994053593</v>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.4328660984166497</v>
+        <v>0.4222404733360525</v>
       </c>
       <c r="H241" s="2" t="n">
-        <v>6.843608358481996</v>
+        <v>6.675617340285701</v>
       </c>
     </row>
     <row r="242">
@@ -30231,16 +30231,16 @@
         </is>
       </c>
       <c r="E242" s="2" t="n">
-        <v>6.909026239142138</v>
+        <v>6.896674534928096</v>
       </c>
       <c r="F242" s="2" t="n">
         <v>6.408965347409231</v>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.5000608917329075</v>
+        <v>0.4877091875188659</v>
       </c>
       <c r="H242" s="2" t="n">
-        <v>7.802521384127203</v>
+        <v>7.609795982373633</v>
       </c>
     </row>
     <row r="243">
@@ -30265,16 +30265,16 @@
         </is>
       </c>
       <c r="E243" s="2" t="n">
-        <v>5.746074505729546</v>
+        <v>5.740364668284071</v>
       </c>
       <c r="F243" s="2" t="n">
         <v>5.529133530428459</v>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.2169409753010871</v>
+        <v>0.211231137855612</v>
       </c>
       <c r="H243" s="2" t="n">
-        <v>3.923598048540458</v>
+        <v>3.820329834559872</v>
       </c>
     </row>
     <row r="244">
@@ -30299,16 +30299,16 @@
         </is>
       </c>
       <c r="E244" s="2" t="n">
-        <v>5.860853151096893</v>
+        <v>5.851862908654754</v>
       </c>
       <c r="F244" s="2" t="n">
         <v>5.52418455151225</v>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.3366685995846428</v>
+        <v>0.3276783571425037</v>
       </c>
       <c r="H244" s="2" t="n">
-        <v>6.09444880860252</v>
+        <v>5.931705468688613</v>
       </c>
     </row>
     <row r="245">
@@ -30945,16 +30945,16 @@
         </is>
       </c>
       <c r="E263" s="2" t="n">
-        <v>73.99568751962109</v>
+        <v>74.02251137290011</v>
       </c>
       <c r="F263" s="2" t="n">
         <v>79.26084715580807</v>
       </c>
       <c r="G263" s="2" t="n">
-        <v>-5.265159636186979</v>
+        <v>-5.238335782907953</v>
       </c>
       <c r="H263" s="2" t="n">
-        <v>-6.642825335738491</v>
+        <v>-6.608982834375494</v>
       </c>
     </row>
     <row r="264">
@@ -30979,16 +30979,16 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>61.91766292428422</v>
+        <v>61.9455101819997</v>
       </c>
       <c r="F264" s="2" t="n">
         <v>65.79733757698776</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>-3.879674652703535</v>
+        <v>-3.851827394988057</v>
       </c>
       <c r="H264" s="2" t="n">
-        <v>-5.896400668437424</v>
+        <v>-5.854077895600461</v>
       </c>
     </row>
     <row r="265">
@@ -31013,16 +31013,16 @@
         </is>
       </c>
       <c r="E265" s="2" t="n">
-        <v>75.69918294379477</v>
+        <v>75.70785894192952</v>
       </c>
       <c r="F265" s="2" t="n">
         <v>77.83872332501248</v>
       </c>
       <c r="G265" s="2" t="n">
-        <v>-2.139540381217714</v>
+        <v>-2.130864383082965</v>
       </c>
       <c r="H265" s="2" t="n">
-        <v>-2.748683803926419</v>
+        <v>-2.737537683121582</v>
       </c>
     </row>
     <row r="266">
@@ -31047,16 +31047,16 @@
         </is>
       </c>
       <c r="E266" s="2" t="n">
-        <v>69.04803309476527</v>
+        <v>69.05810796778231</v>
       </c>
       <c r="F266" s="2" t="n">
         <v>70.9407113712839</v>
       </c>
       <c r="G266" s="2" t="n">
-        <v>-1.892678276518623</v>
+        <v>-1.882603403501591</v>
       </c>
       <c r="H266" s="2" t="n">
-        <v>-2.667971944364743</v>
+        <v>-2.653770123122349</v>
       </c>
     </row>
     <row r="267">
@@ -31081,16 +31081,16 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>53.69737955742512</v>
+        <v>53.71750653067743</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>56.53628859169093</v>
       </c>
       <c r="G267" s="2" t="n">
-        <v>-2.838909034265811</v>
+        <v>-2.818782061013501</v>
       </c>
       <c r="H267" s="2" t="n">
-        <v>-5.021392639988473</v>
+        <v>-4.985792543566034</v>
       </c>
     </row>
     <row r="268">
@@ -31115,16 +31115,16 @@
         </is>
       </c>
       <c r="E268" s="2" t="n">
-        <v>72.88573654308946</v>
+        <v>72.90297511127595</v>
       </c>
       <c r="F268" s="2" t="n">
         <v>76.22263915610104</v>
       </c>
       <c r="G268" s="2" t="n">
-        <v>-3.336902613011574</v>
+        <v>-3.319664044825089</v>
       </c>
       <c r="H268" s="2" t="n">
-        <v>-4.377836624336407</v>
+        <v>-4.355220550716624</v>
       </c>
     </row>
     <row r="269">
@@ -31149,16 +31149,16 @@
         </is>
       </c>
       <c r="E269" s="2" t="n">
-        <v>71.18222826852245</v>
+        <v>71.20408863469163</v>
       </c>
       <c r="F269" s="2" t="n">
         <v>75.08612067394789</v>
       </c>
       <c r="G269" s="2" t="n">
-        <v>-3.903892405425438</v>
+        <v>-3.882032039256259</v>
       </c>
       <c r="H269" s="2" t="n">
-        <v>-5.199219736464484</v>
+        <v>-5.17010601215303</v>
       </c>
     </row>
     <row r="270">
@@ -31183,16 +31183,16 @@
         </is>
       </c>
       <c r="E270" s="2" t="n">
-        <v>78.52254210216036</v>
+        <v>78.52839780357866</v>
       </c>
       <c r="F270" s="2" t="n">
         <v>80.31218971302886</v>
       </c>
       <c r="G270" s="2" t="n">
-        <v>-1.789647610868499</v>
+        <v>-1.783791909450201</v>
       </c>
       <c r="H270" s="2" t="n">
-        <v>-2.228363611132083</v>
+        <v>-2.221072437227821</v>
       </c>
     </row>
     <row r="271">
@@ -31217,16 +31217,16 @@
         </is>
       </c>
       <c r="E271" s="2" t="n">
-        <v>75.56140432191626</v>
+        <v>75.57389221326569</v>
       </c>
       <c r="F271" s="2" t="n">
         <v>78.46860129541943</v>
       </c>
       <c r="G271" s="2" t="n">
-        <v>-2.907196973503176</v>
+        <v>-2.894709082153739</v>
       </c>
       <c r="H271" s="2" t="n">
-        <v>-3.704917540913122</v>
+        <v>-3.689003033526374</v>
       </c>
     </row>
     <row r="272">
@@ -31863,16 +31863,16 @@
         </is>
       </c>
       <c r="E290" s="2" t="n">
-        <v>26.00431248037894</v>
+        <v>25.97748862709991</v>
       </c>
       <c r="F290" s="2" t="n">
         <v>20.73915284419193</v>
       </c>
       <c r="G290" s="2" t="n">
-        <v>5.265159636187001</v>
+        <v>5.238335782907971</v>
       </c>
       <c r="H290" s="2" t="n">
-        <v>25.38753475488043</v>
+        <v>25.25819556016717</v>
       </c>
     </row>
     <row r="291">
@@ -31897,16 +31897,16 @@
         </is>
       </c>
       <c r="E291" s="2" t="n">
-        <v>38.08233707571578</v>
+        <v>38.05448981800031</v>
       </c>
       <c r="F291" s="2" t="n">
         <v>34.20266242301224</v>
       </c>
       <c r="G291" s="2" t="n">
-        <v>3.879674652703542</v>
+        <v>3.851827394988064</v>
       </c>
       <c r="H291" s="2" t="n">
-        <v>11.34319487974486</v>
+        <v>11.26177648789258</v>
       </c>
     </row>
     <row r="292">
@@ -31931,16 +31931,16 @@
         </is>
       </c>
       <c r="E292" s="2" t="n">
-        <v>24.30081705620524</v>
+        <v>24.2921410580705</v>
       </c>
       <c r="F292" s="2" t="n">
         <v>22.16127667498752</v>
       </c>
       <c r="G292" s="2" t="n">
-        <v>2.139540381217721</v>
+        <v>2.130864383082983</v>
       </c>
       <c r="H292" s="2" t="n">
-        <v>9.654409412398739</v>
+        <v>9.615260051727969</v>
       </c>
     </row>
     <row r="293">
@@ -31965,16 +31965,16 @@
         </is>
       </c>
       <c r="E293" s="2" t="n">
-        <v>30.95196690523475</v>
+        <v>30.94189203221768</v>
       </c>
       <c r="F293" s="2" t="n">
         <v>29.0592886287161</v>
       </c>
       <c r="G293" s="2" t="n">
-        <v>1.892678276518648</v>
+        <v>1.882603403501577</v>
       </c>
       <c r="H293" s="2" t="n">
-        <v>6.513161078032454</v>
+        <v>6.478491017296295</v>
       </c>
     </row>
     <row r="294">
@@ -31999,16 +31999,16 @@
         </is>
       </c>
       <c r="E294" s="2" t="n">
-        <v>46.30262044257488</v>
+        <v>46.28249346932256</v>
       </c>
       <c r="F294" s="2" t="n">
         <v>43.46371140830907</v>
       </c>
       <c r="G294" s="2" t="n">
-        <v>2.838909034265811</v>
+        <v>2.818782061013493</v>
       </c>
       <c r="H294" s="2" t="n">
-        <v>6.531676523425216</v>
+        <v>6.485368988702193</v>
       </c>
     </row>
     <row r="295">
@@ -32033,16 +32033,16 @@
         </is>
       </c>
       <c r="E295" s="2" t="n">
-        <v>27.11426345691053</v>
+        <v>27.09702488872405</v>
       </c>
       <c r="F295" s="2" t="n">
         <v>23.77736084389895</v>
       </c>
       <c r="G295" s="2" t="n">
-        <v>3.336902613011578</v>
+        <v>3.319664044825092</v>
       </c>
       <c r="H295" s="2" t="n">
-        <v>14.03394865779562</v>
+        <v>13.96144873528673</v>
       </c>
     </row>
     <row r="296">
@@ -32067,16 +32067,16 @@
         </is>
       </c>
       <c r="E296" s="2" t="n">
-        <v>28.81777173147754</v>
+        <v>28.79591136530838</v>
       </c>
       <c r="F296" s="2" t="n">
         <v>24.9138793260521</v>
       </c>
       <c r="G296" s="2" t="n">
-        <v>3.903892405425438</v>
+        <v>3.882032039256273</v>
       </c>
       <c r="H296" s="2" t="n">
-        <v>15.66954850480949</v>
+        <v>15.58180477817794</v>
       </c>
     </row>
     <row r="297">
@@ -32101,16 +32101,16 @@
         </is>
       </c>
       <c r="E297" s="2" t="n">
-        <v>21.47745789783966</v>
+        <v>21.47160219642134</v>
       </c>
       <c r="F297" s="2" t="n">
         <v>19.68781028697114</v>
       </c>
       <c r="G297" s="2" t="n">
-        <v>1.789647610868514</v>
+        <v>1.783791909450198</v>
       </c>
       <c r="H297" s="2" t="n">
-        <v>9.090130313033612</v>
+        <v>9.060387536498475</v>
       </c>
     </row>
     <row r="298">
@@ -32135,16 +32135,16 @@
         </is>
       </c>
       <c r="E298" s="2" t="n">
-        <v>24.43859567808376</v>
+        <v>24.4261077867343</v>
       </c>
       <c r="F298" s="2" t="n">
         <v>21.53139870458057</v>
       </c>
       <c r="G298" s="2" t="n">
-        <v>2.90719697350319</v>
+        <v>2.894709082153735</v>
       </c>
       <c r="H298" s="2" t="n">
-        <v>13.50212781524832</v>
+        <v>13.44412930098182</v>
       </c>
     </row>
     <row r="299">
@@ -32781,16 +32781,16 @@
         </is>
       </c>
       <c r="E317" s="2" t="n">
-        <v>130480.771620463</v>
+        <v>130486.0827273468</v>
       </c>
       <c r="F317" s="2" t="n">
         <v>278761.4368469829</v>
       </c>
       <c r="G317" s="2" t="n">
-        <v>-148280.6652265198</v>
+        <v>-148275.3541196361</v>
       </c>
       <c r="H317" s="2" t="n">
-        <v>-53.19267503557666</v>
+        <v>-53.19076978392354</v>
       </c>
     </row>
     <row r="318">
@@ -32815,16 +32815,16 @@
         </is>
       </c>
       <c r="E318" s="2" t="n">
-        <v>60372.1001488947</v>
+        <v>60373.69348095982</v>
       </c>
       <c r="F318" s="2" t="n">
         <v>104856.2997168507</v>
       </c>
       <c r="G318" s="2" t="n">
-        <v>-44484.19956795595</v>
+        <v>-44482.60623589083</v>
       </c>
       <c r="H318" s="2" t="n">
-        <v>-42.42396469079982</v>
+        <v>-42.42244515208882</v>
       </c>
     </row>
     <row r="319">
@@ -32849,16 +32849,16 @@
         </is>
       </c>
       <c r="E319" s="2" t="n">
-        <v>178331.2335273424</v>
+        <v>178333.0924147516</v>
       </c>
       <c r="F319" s="2" t="n">
         <v>230229.4663566243</v>
       </c>
       <c r="G319" s="2" t="n">
-        <v>-51898.23282928191</v>
+        <v>-51896.37394187265</v>
       </c>
       <c r="H319" s="2" t="n">
-        <v>-22.54195939840811</v>
+        <v>-22.54115199202409</v>
       </c>
     </row>
     <row r="320">
@@ -32883,16 +32883,16 @@
         </is>
       </c>
       <c r="E320" s="2" t="n">
-        <v>92228.50207456989</v>
+        <v>92229.38725905052</v>
       </c>
       <c r="F320" s="2" t="n">
         <v>116941.9462789899</v>
       </c>
       <c r="G320" s="2" t="n">
-        <v>-24713.44420441998</v>
+        <v>-24712.55901993935</v>
       </c>
       <c r="H320" s="2" t="n">
-        <v>-21.13308781902843</v>
+        <v>-21.13233087551176</v>
       </c>
     </row>
     <row r="321">
@@ -32917,16 +32917,16 @@
         </is>
       </c>
       <c r="E321" s="2" t="n">
-        <v>40826.46614562507</v>
+        <v>40827.26281165763</v>
       </c>
       <c r="F321" s="2" t="n">
         <v>63068.56592960305</v>
       </c>
       <c r="G321" s="2" t="n">
-        <v>-22242.09978397798</v>
+        <v>-22241.30311794542</v>
       </c>
       <c r="H321" s="2" t="n">
-        <v>-35.26653802276803</v>
+        <v>-35.26527484828352</v>
       </c>
     </row>
     <row r="322">
@@ -32951,16 +32951,16 @@
         </is>
       </c>
       <c r="E322" s="2" t="n">
-        <v>122117.5116210804</v>
+        <v>122119.9016191781</v>
       </c>
       <c r="F322" s="2" t="n">
         <v>188843.8109730143</v>
       </c>
       <c r="G322" s="2" t="n">
-        <v>-66726.29935193392</v>
+        <v>-66723.90935383622</v>
       </c>
       <c r="H322" s="2" t="n">
-        <v>-35.33412030191929</v>
+        <v>-35.33285470677726</v>
       </c>
     </row>
     <row r="323">
@@ -32985,16 +32985,16 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>107532.294217767</v>
+        <v>107534.9497712089</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>181672.626831027</v>
       </c>
       <c r="G323" s="2" t="n">
-        <v>-74140.33261325995</v>
+        <v>-74137.67705981804</v>
       </c>
       <c r="H323" s="2" t="n">
-        <v>-40.80985336454544</v>
+        <v>-40.80839163996523</v>
       </c>
     </row>
     <row r="324">
@@ -33019,16 +33019,16 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>206819.2000511457</v>
+        <v>206820.9704201069</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>256246.0884599856</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>-49426.88840883996</v>
+        <v>-49425.1180398787</v>
       </c>
       <c r="H324" s="2" t="n">
-        <v>-19.28883625341983</v>
+        <v>-19.28814536718157</v>
       </c>
     </row>
     <row r="325">
@@ -33053,16 +33053,16 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>170014.9224014508</v>
+        <v>170017.5779548927</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>244155.2550147107</v>
       </c>
       <c r="G325" s="2" t="n">
-        <v>-74140.3326132599</v>
+        <v>-74137.67705981803</v>
       </c>
       <c r="H325" s="2" t="n">
-        <v>-30.36606056617247</v>
+        <v>-30.36497291665958</v>
       </c>
     </row>
     <row r="326">
@@ -33699,16 +33699,16 @@
         </is>
       </c>
       <c r="E344" s="2" t="n">
-        <v>251939.394981899</v>
+        <v>252681.5169092165</v>
       </c>
       <c r="F344" s="2" t="n">
         <v>149352.097259798</v>
       </c>
       <c r="G344" s="2" t="n">
-        <v>102587.2977221011</v>
+        <v>103329.4196494185</v>
       </c>
       <c r="H344" s="2" t="n">
-        <v>68.68822038946695</v>
+        <v>69.18511460182376</v>
       </c>
     </row>
     <row r="345">
@@ -33733,16 +33733,16 @@
         </is>
       </c>
       <c r="E345" s="2" t="n">
-        <v>141777.0514231254</v>
+        <v>141986.6081481695</v>
       </c>
       <c r="F345" s="2" t="n">
         <v>111550.6713708246</v>
       </c>
       <c r="G345" s="2" t="n">
-        <v>30226.38005230081</v>
+        <v>30435.9367773449</v>
       </c>
       <c r="H345" s="2" t="n">
-        <v>27.09654696009866</v>
+        <v>27.28440483891632</v>
       </c>
     </row>
     <row r="346">
@@ -33767,16 +33767,16 @@
         </is>
       </c>
       <c r="E346" s="2" t="n">
-        <v>161621.5319620831</v>
+        <v>161885.0550114311</v>
       </c>
       <c r="F346" s="2" t="n">
         <v>125816.2576804183</v>
       </c>
       <c r="G346" s="2" t="n">
-        <v>35805.27428166484</v>
+        <v>36068.79733101281</v>
       </c>
       <c r="H346" s="2" t="n">
-        <v>28.4583844264488</v>
+        <v>28.66783513989899</v>
       </c>
     </row>
     <row r="347">
@@ -33801,16 +33801,16 @@
         </is>
       </c>
       <c r="E347" s="2" t="n">
-        <v>116631.1287162951</v>
+        <v>116746.3279348064</v>
       </c>
       <c r="F347" s="2" t="n">
         <v>100045.2103111386</v>
       </c>
       <c r="G347" s="2" t="n">
-        <v>16585.91840515654</v>
+        <v>16701.11762366783</v>
       </c>
       <c r="H347" s="2" t="n">
-        <v>16.57842324842406</v>
+        <v>16.69357040854599</v>
       </c>
     </row>
     <row r="348">
@@ -33835,16 +33835,16 @@
         </is>
       </c>
       <c r="E348" s="2" t="n">
-        <v>120704.8882655028</v>
+        <v>120802.9312834029</v>
       </c>
       <c r="F348" s="2" t="n">
         <v>106021.4492116349</v>
       </c>
       <c r="G348" s="2" t="n">
-        <v>14683.43905386796</v>
+        <v>14781.48207176798</v>
       </c>
       <c r="H348" s="2" t="n">
-        <v>13.84949853360105</v>
+        <v>13.94197323436119</v>
       </c>
     </row>
     <row r="349">
@@ -33869,16 +33869,16 @@
         </is>
       </c>
       <c r="E349" s="2" t="n">
-        <v>166764.8635764127</v>
+        <v>167090.5967251255</v>
       </c>
       <c r="F349" s="2" t="n">
         <v>120951.0733101686</v>
       </c>
       <c r="G349" s="2" t="n">
-        <v>45813.79026624403</v>
+        <v>46139.52341495687</v>
       </c>
       <c r="H349" s="2" t="n">
-        <v>37.87795264020394</v>
+        <v>38.14726248574581</v>
       </c>
     </row>
     <row r="350">
@@ -33903,16 +33903,16 @@
         </is>
       </c>
       <c r="E350" s="2" t="n">
-        <v>173616.5470168256</v>
+        <v>173979.3974940298</v>
       </c>
       <c r="F350" s="2" t="n">
         <v>122663.9223373849</v>
       </c>
       <c r="G350" s="2" t="n">
-        <v>50952.62467944075</v>
+        <v>51315.47515664488</v>
       </c>
       <c r="H350" s="2" t="n">
-        <v>41.53839507862505</v>
+        <v>41.83420371598961</v>
       </c>
     </row>
     <row r="351">
@@ -33937,16 +33937,16 @@
         </is>
       </c>
       <c r="E351" s="2" t="n">
-        <v>159545.3005310199</v>
+        <v>159795.7967388011</v>
       </c>
       <c r="F351" s="2" t="n">
         <v>125456.7750422743</v>
       </c>
       <c r="G351" s="2" t="n">
-        <v>34088.52548874557</v>
+        <v>34339.02169652682</v>
       </c>
       <c r="H351" s="2" t="n">
-        <v>27.17153017623718</v>
+        <v>27.37119751799441</v>
       </c>
     </row>
     <row r="352">
@@ -33971,16 +33971,16 @@
         </is>
       </c>
       <c r="E352" s="2" t="n">
-        <v>182488.0768569339</v>
+        <v>182861.9702936514</v>
       </c>
       <c r="F352" s="2" t="n">
         <v>131272.0053184592</v>
       </c>
       <c r="G352" s="2" t="n">
-        <v>51216.0715384747</v>
+        <v>51589.96497519218</v>
       </c>
       <c r="H352" s="2" t="n">
-        <v>39.01522751498091</v>
+        <v>39.30005095148624</v>
       </c>
     </row>
     <row r="353">
@@ -34617,16 +34617,16 @@
         </is>
       </c>
       <c r="E371" s="2" t="n">
-        <v>65.88025867471156</v>
+        <v>65.9454288799174</v>
       </c>
       <c r="F371" s="2" t="n">
         <v>34.88609571089764</v>
       </c>
       <c r="G371" s="2" t="n">
-        <v>30.99416296381391</v>
+        <v>31.05933316901976</v>
       </c>
       <c r="H371" s="2" t="n">
-        <v>88.84388560033683</v>
+        <v>89.0306941378869</v>
       </c>
     </row>
     <row r="372">
@@ -34651,16 +34651,16 @@
         </is>
       </c>
       <c r="E372" s="2" t="n">
-        <v>70.13487334504799</v>
+        <v>70.16524832444252</v>
       </c>
       <c r="F372" s="2" t="n">
         <v>51.54670887456342</v>
       </c>
       <c r="G372" s="2" t="n">
-        <v>18.58816447048457</v>
+        <v>18.61853944987909</v>
       </c>
       <c r="H372" s="2" t="n">
-        <v>36.0608172205873</v>
+        <v>36.11974431808336</v>
       </c>
     </row>
     <row r="373">
@@ -34685,16 +34685,16 @@
         </is>
       </c>
       <c r="E373" s="2" t="n">
-        <v>47.54234951711563</v>
+        <v>47.58272192007493</v>
       </c>
       <c r="F373" s="2" t="n">
         <v>35.33710677770379</v>
       </c>
       <c r="G373" s="2" t="n">
-        <v>12.20524273941184</v>
+        <v>12.24561514237114</v>
       </c>
       <c r="H373" s="2" t="n">
-        <v>34.53945116727223</v>
+        <v>34.65370048375779</v>
       </c>
     </row>
     <row r="374">
@@ -34719,16 +34719,16 @@
         </is>
       </c>
       <c r="E374" s="2" t="n">
-        <v>55.8418724933398</v>
+        <v>55.86597841117871</v>
       </c>
       <c r="F374" s="2" t="n">
         <v>46.10651242373578</v>
       </c>
       <c r="G374" s="2" t="n">
-        <v>9.73536006960402</v>
+        <v>9.75946598744293</v>
       </c>
       <c r="H374" s="2" t="n">
-        <v>21.11493487109258</v>
+        <v>21.16721797942524</v>
       </c>
     </row>
     <row r="375">
@@ -34753,16 +34753,16 @@
         </is>
       </c>
       <c r="E375" s="2" t="n">
-        <v>74.72536134271866</v>
+        <v>74.7403243309566</v>
       </c>
       <c r="F375" s="2" t="n">
         <v>62.70118854923339</v>
       </c>
       <c r="G375" s="2" t="n">
-        <v>12.02417279348527</v>
+        <v>12.03913578172321</v>
       </c>
       <c r="H375" s="2" t="n">
-        <v>19.17694555988171</v>
+        <v>19.20080952256591</v>
       </c>
     </row>
     <row r="376">
@@ -34787,16 +34787,16 @@
         </is>
       </c>
       <c r="E376" s="2" t="n">
-        <v>57.7276005372099</v>
+        <v>57.7747342097537</v>
       </c>
       <c r="F376" s="2" t="n">
         <v>39.04230813560093</v>
       </c>
       <c r="G376" s="2" t="n">
-        <v>18.68529240160896</v>
+        <v>18.73242607415276</v>
       </c>
       <c r="H376" s="2" t="n">
-        <v>47.85908747175396</v>
+        <v>47.97981207743069</v>
       </c>
     </row>
     <row r="377">
@@ -34821,16 +34821,16 @@
         </is>
       </c>
       <c r="E377" s="2" t="n">
-        <v>61.75253871025515</v>
+        <v>61.80125424659402</v>
       </c>
       <c r="F377" s="2" t="n">
         <v>40.30535362004972</v>
       </c>
       <c r="G377" s="2" t="n">
-        <v>21.44718509020543</v>
+        <v>21.4959006265443</v>
       </c>
       <c r="H377" s="2" t="n">
-        <v>53.21175269266617</v>
+        <v>53.33261886046636</v>
       </c>
     </row>
     <row r="378">
@@ -34855,16 +34855,16 @@
         </is>
       </c>
       <c r="E378" s="2" t="n">
-        <v>43.54824233174804</v>
+        <v>43.58660351983806</v>
       </c>
       <c r="F378" s="2" t="n">
         <v>32.86765362228716</v>
       </c>
       <c r="G378" s="2" t="n">
-        <v>10.68058870946088</v>
+        <v>10.71894989755091</v>
       </c>
       <c r="H378" s="2" t="n">
-        <v>32.49574439417391</v>
+        <v>32.61245850017878</v>
       </c>
     </row>
     <row r="379">
@@ -34889,16 +34889,16 @@
         </is>
       </c>
       <c r="E379" s="2" t="n">
-        <v>51.76922671320879</v>
+        <v>51.81994003371825</v>
       </c>
       <c r="F379" s="2" t="n">
         <v>34.96602915887432</v>
       </c>
       <c r="G379" s="2" t="n">
-        <v>16.80319755433447</v>
+        <v>16.85391087484393</v>
       </c>
       <c r="H379" s="2" t="n">
-        <v>48.05577859008861</v>
+        <v>48.20081456280096</v>
       </c>
     </row>
     <row r="380">
@@ -35535,16 +35535,16 @@
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>3704.079094884406</v>
+        <v>3701.95485690463</v>
       </c>
       <c r="F398" s="2" t="n">
         <v>3677.240337235847</v>
       </c>
       <c r="G398" s="2" t="n">
-        <v>26.83875764855884</v>
+        <v>24.7145196687834</v>
       </c>
       <c r="H398" s="2" t="n">
-        <v>0.7298613956990727</v>
+        <v>0.6720942174631183</v>
       </c>
     </row>
     <row r="399">
@@ -35569,16 +35569,16 @@
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>9622.83901407904</v>
+        <v>9622.225269525754</v>
       </c>
       <c r="F399" s="2" t="n">
         <v>9615.206770797251</v>
       </c>
       <c r="G399" s="2" t="n">
-        <v>7.63224328178876</v>
+        <v>7.018498728502891</v>
       </c>
       <c r="H399" s="2" t="n">
-        <v>0.07937679827093233</v>
+        <v>0.07299373685669526</v>
       </c>
     </row>
     <row r="400">
@@ -35603,16 +35603,16 @@
         </is>
       </c>
       <c r="E400" s="2" t="n">
-        <v>6093.479727533617</v>
+        <v>6092.743972529101</v>
       </c>
       <c r="F400" s="2" t="n">
         <v>6084.149291107275</v>
       </c>
       <c r="G400" s="2" t="n">
-        <v>9.330436426342203</v>
+        <v>8.594681421825953</v>
       </c>
       <c r="H400" s="2" t="n">
-        <v>0.1533564674354683</v>
+        <v>0.1412634866535594</v>
       </c>
     </row>
     <row r="401">
@@ -35637,16 +35637,16 @@
         </is>
       </c>
       <c r="E401" s="2" t="n">
-        <v>10771.80192826965</v>
+        <v>10771.47691968621</v>
       </c>
       <c r="F401" s="2" t="n">
         <v>10767.63931828295</v>
       </c>
       <c r="G401" s="2" t="n">
-        <v>4.162609986693496</v>
+        <v>3.837601403254666</v>
       </c>
       <c r="H401" s="2" t="n">
-        <v>0.03865851988212102</v>
+        <v>0.03564013698655932</v>
       </c>
     </row>
     <row r="402">
@@ -35671,16 +35671,16 @@
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>11054.64630512914</v>
+        <v>11054.37384916945</v>
       </c>
       <c r="F402" s="2" t="n">
         <v>11051.15608848863</v>
       </c>
       <c r="G402" s="2" t="n">
-        <v>3.490216640517247</v>
+        <v>3.217760680823631</v>
       </c>
       <c r="H402" s="2" t="n">
-        <v>0.03158236670055553</v>
+        <v>0.02911695984617748</v>
       </c>
     </row>
     <row r="403">
@@ -35705,16 +35705,16 @@
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>8271.662985076875</v>
+        <v>8270.722218562336</v>
       </c>
       <c r="F403" s="2" t="n">
         <v>8259.80159767357</v>
       </c>
       <c r="G403" s="2" t="n">
-        <v>11.86138740330534</v>
+        <v>10.92062088876628</v>
       </c>
       <c r="H403" s="2" t="n">
-        <v>0.1436037810720077</v>
+        <v>0.1322140823799224</v>
       </c>
     </row>
     <row r="404">
@@ -35739,16 +35739,16 @@
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>7836.038304389906</v>
+        <v>7834.99202846594</v>
       </c>
       <c r="F404" s="2" t="n">
         <v>7822.841494812981</v>
       </c>
       <c r="G404" s="2" t="n">
-        <v>13.19680957692435</v>
+        <v>12.15053365295898</v>
       </c>
       <c r="H404" s="2" t="n">
-        <v>0.1686958579650967</v>
+        <v>0.1553212302846162</v>
       </c>
     </row>
     <row r="405">
@@ -35773,16 +35773,16 @@
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>6784.30799047617</v>
+        <v>6783.604595166011</v>
       </c>
       <c r="F405" s="2" t="n">
         <v>6775.39805594684</v>
       </c>
       <c r="G405" s="2" t="n">
-        <v>8.909934529329803</v>
+        <v>8.206539219170736</v>
       </c>
       <c r="H405" s="2" t="n">
-        <v>0.1315042224199574</v>
+        <v>0.1211226137771753</v>
       </c>
     </row>
     <row r="406">
@@ -35807,16 +35807,16 @@
         </is>
       </c>
       <c r="E406" s="2" t="n">
-        <v>5605.035739543056</v>
+        <v>5603.979241147083</v>
       </c>
       <c r="F406" s="2" t="n">
         <v>5591.662078354564</v>
       </c>
       <c r="G406" s="2" t="n">
-        <v>13.37366118849241</v>
+        <v>12.3171627925185</v>
       </c>
       <c r="H406" s="2" t="n">
-        <v>0.2391714842758849</v>
+        <v>0.2202773096786103</v>
       </c>
     </row>
     <row r="407">
@@ -36453,16 +36453,16 @@
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>2.061934893239426</v>
+        <v>2.057809168115604</v>
       </c>
       <c r="F425" s="2" t="n">
         <v>2.047587769303457</v>
       </c>
       <c r="G425" s="2" t="n">
-        <v>0.01434712393596849</v>
+        <v>0.0102213988121469</v>
       </c>
       <c r="H425" s="2" t="n">
-        <v>0.7006841978182479</v>
+        <v>0.4991922185403551</v>
       </c>
     </row>
     <row r="426">
@@ -36487,16 +36487,16 @@
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>4.307353992646417</v>
+        <v>4.306172141541373</v>
       </c>
       <c r="F426" s="2" t="n">
         <v>4.302767115535392</v>
       </c>
       <c r="G426" s="2" t="n">
-        <v>0.004586877111025345</v>
+        <v>0.003405026005980361</v>
       </c>
       <c r="H426" s="2" t="n">
-        <v>0.1066029600919872</v>
+        <v>0.07913572625593226</v>
       </c>
     </row>
     <row r="427">
@@ -36521,16 +36521,16 @@
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>11.32297350211164</v>
+        <v>11.32153073903026</v>
       </c>
       <c r="F427" s="2" t="n">
         <v>11.31794924311563</v>
       </c>
       <c r="G427" s="2" t="n">
-        <v>0.005024258996011</v>
+        <v>0.003581495914627197</v>
       </c>
       <c r="H427" s="2" t="n">
-        <v>0.04439195553971145</v>
+        <v>0.03164438925899685</v>
       </c>
     </row>
     <row r="428">
@@ -36555,16 +36555,16 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>4.759078576482628</v>
+        <v>4.758443681425891</v>
       </c>
       <c r="F428" s="2" t="n">
         <v>4.756403549900415</v>
       </c>
       <c r="G428" s="2" t="n">
-        <v>0.002675026582212858</v>
+        <v>0.002040131525475886</v>
       </c>
       <c r="H428" s="2" t="n">
-        <v>0.05624053035341935</v>
+        <v>0.04289231357416257</v>
       </c>
     </row>
     <row r="429">
@@ -36589,16 +36589,16 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>4.860327775129886</v>
+        <v>4.859792308038282</v>
       </c>
       <c r="F429" s="2" t="n">
         <v>4.85780337621708</v>
       </c>
       <c r="G429" s="2" t="n">
-        <v>0.002524398912806092</v>
+        <v>0.001988931821201412</v>
       </c>
       <c r="H429" s="2" t="n">
-        <v>0.05196585199732637</v>
+        <v>0.04094302850829368</v>
       </c>
     </row>
     <row r="430">
@@ -36623,16 +36623,16 @@
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>4.028248316672186</v>
+        <v>4.026427278222913</v>
       </c>
       <c r="F430" s="2" t="n">
         <v>4.021594878285756</v>
       </c>
       <c r="G430" s="2" t="n">
-        <v>0.0066534383864294</v>
+        <v>0.004832399937156673</v>
       </c>
       <c r="H430" s="2" t="n">
-        <v>0.1654427804837839</v>
+        <v>0.1201612813674691</v>
       </c>
     </row>
     <row r="431">
@@ -36657,16 +36657,16 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>3.74977192431714</v>
+        <v>3.747745416564731</v>
       </c>
       <c r="F431" s="2" t="n">
         <v>3.74240874402789</v>
       </c>
       <c r="G431" s="2" t="n">
-        <v>0.007363180289249982</v>
+        <v>0.00533667253684067</v>
       </c>
       <c r="H431" s="2" t="n">
-        <v>0.1967497617944618</v>
+        <v>0.1425999376833676</v>
       </c>
     </row>
     <row r="432">
@@ -36691,16 +36691,16 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>10.47565804818722</v>
+        <v>10.47428179802327</v>
       </c>
       <c r="F432" s="2" t="n">
         <v>10.47085433312493</v>
       </c>
       <c r="G432" s="2" t="n">
-        <v>0.004803715062283942</v>
+        <v>0.003427464898335231</v>
       </c>
       <c r="H432" s="2" t="n">
-        <v>0.04587701165020711</v>
+        <v>0.03273338344028261</v>
       </c>
     </row>
     <row r="433">
@@ -36725,16 +36725,16 @@
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>9.077332947982349</v>
+        <v>9.075270811716141</v>
       </c>
       <c r="F433" s="2" t="n">
         <v>9.070155408227055</v>
       </c>
       <c r="G433" s="2" t="n">
-        <v>0.007177539755293338</v>
+        <v>0.005115403489085679</v>
       </c>
       <c r="H433" s="2" t="n">
-        <v>0.07913359178810733</v>
+        <v>0.05639819009546153</v>
       </c>
     </row>
     <row r="434">
@@ -37371,16 +37371,16 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>48.51890324169861</v>
+        <v>48.57073231935405</v>
       </c>
       <c r="F452" s="2" t="n">
         <v>47.34518971380331</v>
       </c>
       <c r="G452" s="2" t="n">
-        <v>1.173713527895295</v>
+        <v>1.225542605550736</v>
       </c>
       <c r="H452" s="2" t="n">
-        <v>2.47905549643009</v>
+        <v>2.588526126854727</v>
       </c>
     </row>
     <row r="453">
@@ -37405,16 +37405,16 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>52.39458487353753</v>
+        <v>52.40893833359175</v>
       </c>
       <c r="F453" s="2" t="n">
         <v>52.10083830325514</v>
       </c>
       <c r="G453" s="2" t="n">
-        <v>0.2937465702823872</v>
+        <v>0.3081000303366039</v>
       </c>
       <c r="H453" s="2" t="n">
-        <v>0.5638039230244679</v>
+        <v>0.5913533071066814</v>
       </c>
     </row>
     <row r="454">
@@ -37439,16 +37439,16 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>97.87629849462417</v>
+        <v>97.89509101845073</v>
       </c>
       <c r="F454" s="2" t="n">
         <v>97.47217568128711</v>
       </c>
       <c r="G454" s="2" t="n">
-        <v>0.4041228133370538</v>
+        <v>0.4229153371636158</v>
       </c>
       <c r="H454" s="2" t="n">
-        <v>0.414603255249424</v>
+        <v>0.4338831407092598</v>
       </c>
     </row>
     <row r="455">
@@ -37473,16 +37473,16 @@
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>71.50936990028188</v>
+        <v>71.51752319984799</v>
       </c>
       <c r="F455" s="2" t="n">
         <v>71.36213347829926</v>
       </c>
       <c r="G455" s="2" t="n">
-        <v>0.1472364219826261</v>
+        <v>0.1553897215487297</v>
       </c>
       <c r="H455" s="2" t="n">
-        <v>0.2063228981619498</v>
+        <v>0.217748144533799</v>
       </c>
     </row>
     <row r="456">
@@ -37507,16 +37507,16 @@
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>53.99692550424508</v>
+        <v>54.00395783543333</v>
       </c>
       <c r="F456" s="2" t="n">
         <v>53.89607148085827</v>
       </c>
       <c r="G456" s="2" t="n">
-        <v>0.1008540233868089</v>
+        <v>0.1078863545750579</v>
       </c>
       <c r="H456" s="2" t="n">
-        <v>0.1871268547330546</v>
+        <v>0.2001748023756701</v>
       </c>
     </row>
     <row r="457">
@@ -37541,16 +37541,16 @@
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>72.47195032017014</v>
+        <v>72.49452952571609</v>
       </c>
       <c r="F457" s="2" t="n">
         <v>71.97737777040193</v>
       </c>
       <c r="G457" s="2" t="n">
-        <v>0.4945725497682076</v>
+        <v>0.5171517553141598</v>
       </c>
       <c r="H457" s="2" t="n">
-        <v>0.6871222112950919</v>
+        <v>0.7184920753348416</v>
       </c>
     </row>
     <row r="458">
@@ -37575,16 +37575,16 @@
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>63.37592565362624</v>
+        <v>63.40111260549658</v>
       </c>
       <c r="F458" s="2" t="n">
         <v>62.82273170482901</v>
       </c>
       <c r="G458" s="2" t="n">
-        <v>0.5531939487972295</v>
+        <v>0.5783809006675682</v>
       </c>
       <c r="H458" s="2" t="n">
-        <v>0.8805633467140478</v>
+        <v>0.920655445842559</v>
       </c>
     </row>
     <row r="459">
@@ -37609,16 +37609,16 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>112.3901276188296</v>
+        <v>112.40790686915</v>
       </c>
       <c r="F459" s="2" t="n">
         <v>112.0042931839721</v>
       </c>
       <c r="G459" s="2" t="n">
-        <v>0.3858344348575002</v>
+        <v>0.4036136851778593</v>
       </c>
       <c r="H459" s="2" t="n">
-        <v>0.3444818264454825</v>
+        <v>0.3603555486171459</v>
       </c>
     </row>
     <row r="460">
@@ -37643,16 +37643,16 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>87.81095584802875</v>
+        <v>87.83735557373143</v>
       </c>
       <c r="F460" s="2" t="n">
         <v>87.22909070580938</v>
       </c>
       <c r="G460" s="2" t="n">
-        <v>0.581865142219371</v>
+        <v>0.6082648679220455</v>
       </c>
       <c r="H460" s="2" t="n">
-        <v>0.6670540040154509</v>
+        <v>0.6973188221960172</v>
       </c>
     </row>
   </sheetData>
